--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -1358,7 +1358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>96056</v>
+        <v>96059</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>95001</v>
+        <v>95002</v>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
@@ -2419,16 +2419,16 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>비상! 비상!! 전원 출동!!</t>
+          <t>실험은 폭발이다아아!!</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>96057</v>
+        <v>96060</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>95001</v>
+        <v>95002</v>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
@@ -2437,16 +2437,16 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>호루라기 삐이이익!!</t>
+          <t>이번엔 이걸 섞어볼까~?</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>95001</v>
+        <v>95002</v>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
@@ -2455,286 +2455,286 @@
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>경비 30년의 내공을 보여주마!</t>
+          <t>내 몸으로 직접 실험한다!!</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>96059</v>
+        <v>96074</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>95002</v>
+        <v>95001</v>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>실험은 폭발이다아아!!</t>
+          <t>퉁! 퉁! 퉁! 사후르!!</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>96060</v>
+        <v>96075</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>95002</v>
+        <v>95001</v>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>이번엔 이걸 섞어볼까~?</t>
+          <t>사후르 시간이다!!</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>96061</v>
+        <v>96076</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>95002</v>
+        <v>95001</v>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>내 몸으로 직접 실험한다!!</t>
+          <t>퉁퉁퉁퉁퉁퉁퉁퉁퉁 사후르!</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>96062</v>
+        <v>96077</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>95003</v>
+        <v>95001</v>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>결재 올려!! 전부 다!!</t>
+          <t>진압봉 맛 좀 봐라!</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>96063</v>
+        <v>96078</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>95003</v>
+        <v>95002</v>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>이사회 소집이다!!!</t>
+          <t>이븐하게 익혀 드릴게요~</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>96064</v>
+        <v>96079</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>95003</v>
+        <v>95002</v>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>예산은 너희들 몫이 아니다!</t>
+          <t>익힘 정도가 아주 이븐하네요!</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>96065</v>
+        <v>96080</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>95004</v>
+        <v>95002</v>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>냐아아아아앙!!!!</t>
+          <t>쥐 요리는 굽기가 생명이지!</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>96066</v>
+        <v>96081</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>95004</v>
+        <v>95002</v>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>(우다다다다다)</t>
+          <t>숨 참아 봐~ 독가스다!</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>96067</v>
+        <v>96082</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>95004</v>
+        <v>95003</v>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>상자다… 상자다…!!</t>
+          <t>중요한 건 꺾이지 않는 마음!!</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>96068</v>
+        <v>96083</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>95005</v>
+        <v>95003</v>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>하늘이여 무너져라냥!</t>
+          <t>중꺾마다!!</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>96069</v>
+        <v>96084</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>95005</v>
+        <v>95003</v>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>개굴개굴해져라~!</t>
+          <t>이 정도로 꺾일 소장이 아니다!</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>96070</v>
+        <v>96085</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>95005</v>
+        <v>95003</v>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>마법 학교 수석의 힘이다냥!</t>
+          <t>서류는 던지라고 있는 거야!</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>96071</v>
+        <v>96086</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>95006</v>
+        <v>95004</v>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>궤도 포격 허가한다냥!</t>
+          <t>해피해피해피~!</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>96072</v>
+        <v>96087</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>95006</v>
+        <v>95004</v>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>블랙홀 생성 완료.</t>
+          <t>(통 통 통)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>96073</v>
+        <v>96088</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>95006</v>
+        <v>95004</v>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>우주는 넓고 쥐는 작다냥.</t>
+          <t>냥피냥피냥피!</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>96074</v>
+        <v>96089</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>95001</v>
+        <v>95005</v>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
@@ -2743,16 +2743,16 @@
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>퉁! 퉁! 퉁! 사후르!!</t>
+          <t>무한동력이다냥!</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>96075</v>
+        <v>96090</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>95001</v>
+        <v>95005</v>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
@@ -2761,16 +2761,16 @@
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>사후르 시간이다!!</t>
+          <t>식빵이 먼저냐, 고양이가 먼저냐!</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>96076</v>
+        <v>96091</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>95001</v>
+        <v>95005</v>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
@@ -2779,34 +2779,34 @@
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>퉁퉁퉁퉁퉁퉁퉁퉁퉁 사후르!</t>
+          <t>버터 바른 고양이 출동~!</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>96077</v>
+        <v>96092</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>95001</v>
+        <v>95006</v>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>진압봉 맛 좀 봐라!</t>
+          <t>맥스웰 부대, 강하.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>96078</v>
+        <v>96093</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>95002</v>
+        <v>95006</v>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
@@ -2815,16 +2815,16 @@
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>이븐하게 익혀 드릴게요~</t>
+          <t>빙글빙글 맥스웰 투하!</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>96079</v>
+        <v>96094</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>95002</v>
+        <v>95006</v>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
@@ -2833,277 +2833,313 @@
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>익힘 정도가 아주 이븐하네요!</t>
+          <t>(맥스웰 테마 흥얼흥얼)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>96080</v>
+        <v>96095</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>95002</v>
+        <v>95001</v>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>쥐 요리는 굽기가 생명이지!</t>
+          <t>무야호~!!!</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>96081</v>
+        <v>96096</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>95002</v>
+        <v>95001</v>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>숨 참아 봐~ 독가스다!</t>
+          <t>그만큼 신나신다는 거지!!</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>96082</v>
+        <v>96097</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>95003</v>
+        <v>95001</v>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>중요한 건 꺾이지 않는 마음!!</t>
+          <t>관짝 들어갑니다~ (빠밤 빠밤)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>96083</v>
+        <v>96098</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>95003</v>
+        <v>95002</v>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>중꺾마다!!</t>
+          <t>펑?! ...오히려 좋아!!</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>96084</v>
+        <v>96099</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>95003</v>
+        <v>95002</v>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>이 정도로 꺾일 소장이 아니다!</t>
+          <t>실험 실패? 오히려 좋아!!</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>96085</v>
+        <v>96100</v>
       </c>
       <c r="B87" s="1" t="n">
         <v>95003</v>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>서류는 던지라고 있는 거야!</t>
+          <t>이 층, 전액 현금 매입이다!!</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>96086</v>
+        <v>96101</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>95004</v>
+        <v>95003</v>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>해피해피해피~!</t>
+          <t>긴급 회의!! 누가 임포스터지?</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>96087</v>
+        <v>96102</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>95004</v>
+        <v>95003</v>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>(통 통 통)</t>
+          <t>쥐가 임포스터다!! 투표해!!</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>96088</v>
+        <v>96103</v>
       </c>
       <c r="B90" s="1" t="n">
         <v>95004</v>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>냥피냥피냥피!</t>
+          <t>(한강 위를 걷는 고양이)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>96089</v>
+        <v>96104</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>95005</v>
+        <v>95004</v>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>무한동력이다냥!</t>
+          <t>꽁냥꽁냥~!!</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>96090</v>
+        <v>96105</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>95005</v>
+        <v>95004</v>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>식빵이 먼저냐, 고양이가 먼저냐!</t>
+          <t>(엉엉엉엉) 바나나...</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>96091</v>
+        <v>96106</v>
       </c>
       <c r="B93" s="1" t="n">
         <v>95005</v>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>버터 바른 고양이 출동~!</t>
+          <t>트랄랄레로 트랄랄라~!</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>96092</v>
+        <v>96107</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>95006</v>
+        <v>95005</v>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>맥스웰 부대, 강하.</t>
+          <t>발레리나 카푸치나~ 냥!</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>96093</v>
+        <v>96108</v>
       </c>
       <c r="B95" s="1" t="n">
-        <v>95006</v>
+        <v>95005</v>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>빙글빙글 맥스웰 투하!</t>
+          <t>머리를 바꿔 주겠다냥!</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>96094</v>
+        <v>96109</v>
       </c>
       <c r="B96" s="1" t="n">
         <v>95006</v>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>(맥스웰 테마 흥얼흥얼)</t>
+          <t>우리는 답을 찾을 것이다. 늘 그랬듯이.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>96110</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t>No... it's necessary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96111</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>95006</v>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>눈에서 레이저 나간다냥.</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3556,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>[필살] 쥐 무리 3곳에 차례로 경고 원 → 공중 3단 점프 내려찍기</t>
+          <t>[필살] 무야호 (2021 무한도전): 쥐 무리 3곳으로 차례로 높이 점프하며 무야호~!! → 착지 범위 기절</t>
         </is>
       </c>
       <c r="C12" s="1" t="n">
@@ -3540,7 +3576,7 @@
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>3단 공중 내려찍기</t>
+          <t>무야호~!! 3단 점프</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3588,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>[필살] 하늘에서 안전 고깔이 개수만큼 쥐 무리에 떨어짐</t>
+          <t>[필살] 관짝소년단 (2020): 하늘에서 관이 개수만큼 떨어짐 (경고 원) → 착지 범위 기절 → 관이 들썩들썩 운구 댄스</t>
         </is>
       </c>
       <c r="C13" s="1" t="n">
@@ -3572,7 +3608,7 @@
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>안전 고깔 폭격</t>
+          <t>관짝소년단</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3652,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>[필살] 약을 마시고 거대화(공격 길이 초 동안) → 빨라지고 개수만큼 주변 충격파</t>
+          <t>[필살] 오히려 좋아 (2020): 실험 약을 마셨다가 머리가 펑! → "오히려 좋아" 하며 거대화 (dur 초, 커지고 빨라짐, 주기마다 충격파)</t>
         </is>
       </c>
       <c r="C15" s="1" t="n">
@@ -3636,7 +3672,7 @@
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>자가 실험: 거대화!!</t>
+          <t>오히려 좋아!!</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3684,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>[필살] 결재 서류 더미가 개수만큼 쥐 무리에 떨어짐</t>
+          <t>[필살] 전액 현금 매입 (2025): 돈다발이 개수만큼 쥐 무리 위로 떨어짐</t>
         </is>
       </c>
       <c r="C16" s="1" t="n">
@@ -3668,7 +3704,7 @@
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>결재 서류 폭탄</t>
+          <t>전액 현금 매입</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3716,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>[필살] 책상 내리치기 충격파(반경) + 경비원 개수만큼 소집</t>
+          <t>[필살] 어몽어스 비상 회의 (2020): 머리 위 비상 버튼 + 빨간 경보 → 충격파(반경) + 경비원 개수만큼 소환</t>
         </is>
       </c>
       <c r="C17" s="1" t="n">
@@ -3700,7 +3736,7 @@
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>긴급 이사회 소집</t>
+          <t>긴급 비상 회의!!</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3748,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>[필살] 방 안을 개수만큼 미친 듯이 질주, 지나간 길(반경)의 쥐 기절</t>
+          <t>[필살] 꽁냥이 (2021 한강 위를 걷는 고양이 뉴스): 물보라 튀기며 개수만큼 미친 질주, 지나간(반경) 쥐 기절</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
@@ -3732,7 +3768,7 @@
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>새벽 3시 우다다</t>
+          <t>한강 고양이 질주</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3780,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>[필살] 거대 상자에 쏙 들어감(웅크림 초 동안 무적) → 상자 폭발 충격파(반경)</t>
+          <t>[필살] 바나나 고양이 (2023): 바나나 옷 입고 엉엉 (무적, 눈물) → 웅크림 끝에 바나나 폭발 (반경 기절)</t>
         </is>
       </c>
       <c r="C19" s="1" t="n">
@@ -3764,7 +3800,7 @@
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>상자 들어가기</t>
+          <t>바나나 고양이</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3812,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>[필살] 운석이 개수만큼 쥐 무리에 떨어짐</t>
+          <t>[필살] 트랄랄레로 트랄랄라 (2025 이탈리안 브레인롯): 운동화 신은 상어가 개수만큼 떨어짐 → 맞은 쥐 머리가 상어로 (기절)</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
@@ -3796,7 +3832,7 @@
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>운석 소나기</t>
+          <t>트랄랄레로 트랄랄라</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3844,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>[필살] 반경 안 쥐가 개구리가 됨 (개굴! 기절)</t>
+          <t>[필살] 발레리나 카푸치나 (2025 이탈리안 브레인롯): 빙글빙글 돌다가 반경 안 쥐 머리를 커피잔으로 (기절)</t>
         </is>
       </c>
       <c r="C21" s="1" t="n">
@@ -3828,7 +3864,7 @@
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>개구리 저주</t>
+          <t>발레리나 카푸치나</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3876,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>[필살] 궤도 레이저가 개수만큼 쥐 무리를 차례로 포격</t>
+          <t>[필살] 홈랜더 (더 보이즈) 눈 레이저: 보스 눈에서 쥐 무리 개수 곳으로 차례로 빔 → 범위 기절</t>
         </is>
       </c>
       <c r="C22" s="1" t="n">
@@ -3860,7 +3896,7 @@
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>궤도 레이저 포격</t>
+          <t>홈랜더 눈 레이저</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3908,7 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>[필살] 쥐 무리 한가운데 초거대 블랙홀 → 웅크림 초 동안 빨아들인 뒤 띄워서 기절</t>
+          <t>[필살] 인터스텔라 STAY: 초거대 블랙홀이 웅크림 동안 모든 쥐를 빨아들임 → 컷씬 (책장 너머 과거의 자신을 찍찍!! 말림, Boss.cutscene 랜덤 장면) → 사방으로 튕겨 나옴 (기절)</t>
         </is>
       </c>
       <c r="C23" s="1" t="n">
@@ -3885,14 +3921,14 @@
         <v>0</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>초거대 블랙홀</t>
+          <t>STAY</t>
         </is>
       </c>
     </row>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -3154,7 +3154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3164,6 +3164,7 @@
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3207,6 +3208,11 @@
           <t>화면 이름</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>전용 대사</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -3249,6 +3255,11 @@
           <t>atk_name</t>
         </is>
       </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -3291,6 +3302,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3323,6 +3339,7 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I4" s="1" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -3355,6 +3372,7 @@
           <t>내려찍기</t>
         </is>
       </c>
+      <c r="I5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -3387,6 +3405,7 @@
           <t>덮치기</t>
         </is>
       </c>
+      <c r="I6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -3419,6 +3438,7 @@
           <t>플라스크 투척</t>
         </is>
       </c>
+      <c r="I7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -3451,6 +3471,7 @@
           <t>헤어볼</t>
         </is>
       </c>
+      <c r="I8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -3483,6 +3504,7 @@
           <t>불덩이</t>
         </is>
       </c>
+      <c r="I9" s="1" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -3515,6 +3537,7 @@
           <t>휘두르기</t>
         </is>
       </c>
+      <c r="I10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -3547,6 +3570,7 @@
           <t>무중력 파동</t>
         </is>
       </c>
+      <c r="I11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -3579,6 +3603,7 @@
           <t>무야호~!! 3단 점프</t>
         </is>
       </c>
+      <c r="I12" s="1" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3588,17 +3613,17 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>[필살] 관짝소년단 (2020): 하늘에서 관이 개수만큼 떨어짐 (경고 원) → 착지 범위 기절 → 관이 들썩들썩 운구 댄스</t>
+          <t>[필살] 관짝소년단 (2020): 하늘에서 관이 개수만큼 떨어짐 (경고 원) → 착지 범위 기절 → 관 멘 운구단이 나와 두 포즈를 번갈아 춤추며 옆걸음 (Boss 인스펙터 운구단)</t>
         </is>
       </c>
       <c r="C13" s="1" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>1.6</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>0.8</v>
@@ -3611,6 +3636,7 @@
           <t>관짝소년단</t>
         </is>
       </c>
+      <c r="I13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -3643,6 +3669,7 @@
           <t>약품 대방출 파티</t>
         </is>
       </c>
+      <c r="I14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -3675,6 +3702,7 @@
           <t>오히려 좋아!!</t>
         </is>
       </c>
+      <c r="I15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -3707,6 +3735,7 @@
           <t>전액 현금 매입</t>
         </is>
       </c>
+      <c r="I16" s="1" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -3716,7 +3745,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>[필살] 어몽어스 비상 회의 (2020): 머리 위 비상 버튼 + 빨간 경보 → 충격파(반경) + 경비원 개수만큼 소환</t>
+          <t>[필살] 어몽어스 긴급 회의 (2020): 긴급 회의 컷씬 (보스 얼굴) → 머리 위 비상 버튼 + 빨간 경보 → 충격파(반경) + 경비원 개수만큼 소환</t>
         </is>
       </c>
       <c r="C17" s="1" t="n">
@@ -3739,6 +3768,7 @@
           <t>긴급 비상 회의!!</t>
         </is>
       </c>
+      <c r="I17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -3748,7 +3778,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>[필살] 꽁냥이 (2021 한강 위를 걷는 고양이 뉴스): 물보라 튀기며 개수만큼 미친 질주, 지나간(반경) 쥐 기절</t>
+          <t>[필살] 꽁꽁 얼어붙은 한강 위로 고양이가 걸어다닙니다 (2021 뉴스): 보스 둘레(Boss iceRadius)가 얼음 바닥 (쥐가 미끄러져 넘어짐) → 개수만큼 질주, 지나간(반경) 쥐 기절</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
@@ -3768,7 +3798,12 @@
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>한강 고양이 질주</t>
+          <t>꽁꽁 얼어붙은 한강</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>꽁꽁 얼어붙은 한강 위로 고양이가 걸어다닙니다</t>
         </is>
       </c>
     </row>
@@ -3780,29 +3815,30 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>[필살] 바나나 고양이 (2023): 바나나 옷 입고 엉엉 (무적, 눈물) → 웅크림 끝에 바나나 폭발 (반경 기절)</t>
+          <t>[필살] 바나나 고양이 (2023): 웅크림 동안 엉엉 울다가 → 우는 바나나 고양이 개수만큼 소환 → 가까운 쥐에게 아장아장 걸어가 닿거나 시간이 다 되면 펑 (반경 기절)</t>
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>바나나 고양이</t>
-        </is>
-      </c>
+          <t>바나나 고양이 소환</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -3812,7 +3848,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>[필살] 트랄랄레로 트랄랄라 (2025 이탈리안 브레인롯): 운동화 신은 상어가 개수만큼 떨어짐 → 맞은 쥐 머리가 상어로 (기절)</t>
+          <t>[필살] 트랄랄레로 트랄랄라 (2025 이탈리안 브레인롯): 운동화 상어가 개수만큼 떨어짐 → 맞은 쥐 머리가 (기절 시간 동안) 상어 머리로 바뀜</t>
         </is>
       </c>
       <c r="C20" s="1" t="n">
@@ -3835,6 +3871,7 @@
           <t>트랄랄레로 트랄랄라</t>
         </is>
       </c>
+      <c r="I20" s="1" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -3844,7 +3881,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>[필살] 발레리나 카푸치나 (2025 이탈리안 브레인롯): 빙글빙글 돌다가 반경 안 쥐 머리를 커피잔으로 (기절)</t>
+          <t>[필살] 발레리나 카푸치나 (2025 이탈리안 브레인롯): 빙글빙글 돌다가 반경 안 쥐 머리를 (기절 시간 동안) 커피잔으로 바꿈</t>
         </is>
       </c>
       <c r="C21" s="1" t="n">
@@ -3867,6 +3904,7 @@
           <t>발레리나 카푸치나</t>
         </is>
       </c>
+      <c r="I21" s="1" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -3876,7 +3914,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>[필살] 홈랜더 (더 보이즈) 눈 레이저: 보스 눈에서 쥐 무리 개수 곳으로 차례로 빔 → 범위 기절</t>
+          <t>[필살] 홈랜더 (더 보이즈) 눈 레이저: 웅크림 동안 눈이 빨갛게 → 두 눈에서 쥐 무리 개수 곳으로 차례로 굵은 빔 (얌념~) → 범위 기절</t>
         </is>
       </c>
       <c r="C22" s="1" t="n">
@@ -3899,6 +3937,11 @@
           <t>홈랜더 눈 레이저</t>
         </is>
       </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>난 너희들보다 강하고, 똑똑하고, 더 낫다. 난 더 낫다고!</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -3931,6 +3974,7 @@
           <t>STAY</t>
         </is>
       </c>
+      <c r="I23" s="1" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -3963,6 +4007,7 @@
           <t>진압봉 휘두르기</t>
         </is>
       </c>
+      <c r="I24" s="1" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3995,6 +4040,7 @@
           <t>독가스 구름</t>
         </is>
       </c>
+      <c r="I25" s="1" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -4027,6 +4073,7 @@
           <t>서류 가방 던지기</t>
         </is>
       </c>
+      <c r="I26" s="1" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -4059,6 +4106,7 @@
           <t>퉁퉁퉁 사후르</t>
         </is>
       </c>
+      <c r="I27" s="1" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -4091,6 +4139,7 @@
           <t>이븐하게 익혀드릴게요</t>
         </is>
       </c>
+      <c r="I28" s="1" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -4123,6 +4172,11 @@
           <t>중요한 건 꺾이지 않는 마음</t>
         </is>
       </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>중요한 건 꺾이지 않는 마음!!</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -4155,6 +4209,7 @@
           <t>해피해피해피</t>
         </is>
       </c>
+      <c r="I30" s="1" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -4187,6 +4242,7 @@
           <t>무한동력 버터 고양이</t>
         </is>
       </c>
+      <c r="I31" s="1" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -4219,6 +4275,7 @@
           <t>맥스웰 고양이 낙하</t>
         </is>
       </c>
+      <c r="I32" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -848,7 +848,7 @@
         <v>2.8</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>33.4</v>
+        <v>30.1</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>300</v>
@@ -939,7 +939,7 @@
         <v>2.8</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>56</v>
+        <v>33.6</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>300</v>
@@ -1030,7 +1030,7 @@
         <v>2.8</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>70.7</v>
+        <v>42.4</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>300</v>
@@ -1121,7 +1121,7 @@
         <v>3.4</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>56.1</v>
+        <v>50.5</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>300</v>
@@ -1212,7 +1212,7 @@
         <v>3.4</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>53.9</v>
+        <v>48.5</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>300</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>Frog_Curse</t>
+          <t>Invis_Cloak</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1303,7 +1303,7 @@
         <v>3.4</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>36</v>
+        <v>32.4</v>
       </c>
       <c r="M9" s="1" t="n">
         <v>300</v>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>발레리나 카푸치나~ 냥!</t>
+          <t>상어 신발 신고 트랄랄라~ 냥!</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3356,7 +3356,7 @@
         <v>300</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
         <v>280</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
         <v>110</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>3</v>
@@ -3455,7 +3455,7 @@
         <v>110</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>3</v>
@@ -3488,7 +3488,7 @@
         <v>110</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>5</v>
@@ -3521,7 +3521,7 @@
         <v>280</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>2</v>
@@ -3554,7 +3554,7 @@
         <v>360</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>240</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3</v>
@@ -3620,7 +3620,7 @@
         <v>130</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>4</v>
@@ -3653,7 +3653,7 @@
         <v>110</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>14</v>
@@ -3686,7 +3686,7 @@
         <v>230</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>6</v>
@@ -3719,7 +3719,7 @@
         <v>130</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>7</v>
@@ -3752,7 +3752,7 @@
         <v>380</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>6</v>
@@ -3785,7 +3785,7 @@
         <v>120</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>5</v>
@@ -3822,7 +3822,7 @@
         <v>150</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>4</v>
@@ -3855,7 +3855,7 @@
         <v>150</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>8</v>
@@ -3888,7 +3888,7 @@
         <v>340</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>0</v>
@@ -3921,7 +3921,7 @@
         <v>160</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>6</v>
@@ -3958,7 +3958,7 @@
         <v>450</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
         <v>260</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
         <v>140</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>2</v>
@@ -4057,7 +4057,7 @@
         <v>170</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>1</v>
@@ -4090,7 +4090,7 @@
         <v>320</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>3</v>
@@ -4123,7 +4123,7 @@
         <v>170</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>2</v>
@@ -4156,7 +4156,7 @@
         <v>220</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>170</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>6</v>
@@ -4226,7 +4226,7 @@
         <v>70</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>4</v>
@@ -4259,7 +4259,7 @@
         <v>120</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>6</v>
@@ -4276,6 +4276,43 @@
         </is>
       </c>
       <c r="I32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Invis_Cloak</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 투명 망토 (해리포터): 망토를 뒤집어쓰고 사라짐 (피해 안 받음) → 쥐 무리 쪽으로 몰래 이동 → 경고 원 → 그 자리에 나타나며 덮침. 개수만큼 반복, 지속 = 숨어 있는 시간 합</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>투명 망토</t>
+        </is>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>나는 나쁜 짓을 할 것을 엄숙히 맹세한다냥!</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4489,7 +4526,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>체력 = 그 층 적정 전투력(찍찍!!) × 이 값. 적정 전투력은 무리 공격력 합이라, 대략 "적정 무리가 이 초 동안 다 같이 때리는 양"</t>
+          <t>체력 = 그 층 적정 전투력(찍찍!!) × 이 값. 적정 전투력은 무리 공격력 합이라, 대략 "적정 무리가 이 초 동안 다 같이 때리는 양" · 2026-10-12: 보스전 목표 = 스테이지 테이블 boss_sec (허들 층 64.8초 · 10·15층 보통 43.2초)에 맞춰 옛 값(72초 기준) × 비율</t>
         </is>
       </c>
     </row>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -463,105 +463,110 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>보스 이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>그림 코드 id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>리그</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>등장 층</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>공격 타입</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>두 번째 공격</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>두 번째 공격 확률</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>테마 색</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>크기 배율</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>충돌 반경 배율</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>체력 (적정 전투력 × 초)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>치즈 배율</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>걷기 속도</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>공격 간격 최소</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>공격 간격 최대</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>필살 패턴 1 (체력 70%)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>필살 패턴 2 (체력 35%)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>그 뒤 필살 확률</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>쿨타임 스킬</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>스킬 쿨타임 (초)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>첫 스킬 (초)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
@@ -580,105 +585,110 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>boss_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>code_id</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>rig</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>floor</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>atk_type</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>atk2_type</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>atk2_chance</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>color</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>scale</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>radius_mul</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>hp_pow_sec</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>cheese_mul</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>move_speed</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>atk_cd_min</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>atk_cd_max</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>special1_type</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>special2_type</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>special_chance</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>skill_type</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>skill_cd</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>skill_first</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -697,105 +707,110 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="R3" s="1" t="inlineStr">
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="S3" s="1" t="inlineStr">
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="T3" s="1" t="inlineStr">
+      <c r="U3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="U3" s="1" t="inlineStr">
+      <c r="V3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="V3" s="1" t="inlineStr">
+      <c r="W3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="W3" s="1" t="inlineStr">
+      <c r="X3" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -810,83 +825,86 @@
           <t>경비대장 강철수</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="1" t="n">
+        <v>2995001</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>boss_chief</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="F4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Stomp</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Baton</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>#8fb3c7</t>
         </is>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>2.8</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>2.8</v>
       </c>
       <c r="L4" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M4" s="1" t="n">
         <v>30.1</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="N4" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="O4" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="P4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="P4" s="1" t="n">
+      <c r="Q4" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q4" s="1" t="inlineStr">
+      <c r="R4" s="1" t="inlineStr">
         <is>
           <t>Mega_Stomp</t>
         </is>
       </c>
-      <c r="R4" s="1" t="inlineStr">
+      <c r="S4" s="1" t="inlineStr">
         <is>
           <t>Cone_Rain</t>
         </is>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="T4" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="T4" s="1" t="inlineStr">
+      <c r="U4" s="1" t="inlineStr">
         <is>
           <t>Tung_Sahur</t>
         </is>
       </c>
-      <c r="U4" s="1" t="n">
+      <c r="V4" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="V4" s="1" t="n">
+      <c r="W4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="W4" s="1" t="inlineStr">
+      <c r="X4" s="1" t="inlineStr">
         <is>
           <t>5층 보스. 쥐 무리 쪽으로 쿵쿵 걸어와 점프 내려찍기</t>
         </is>
@@ -901,83 +919,86 @@
           <t>광기의 수석 연구원</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="1" t="n">
+        <v>2995002</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>boss_mad</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>Flask</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>Gas_Cloud</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>#9dd5a8</t>
         </is>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>2.8</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>2.8</v>
       </c>
       <c r="L5" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>33.6</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="N5" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="O5" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="P5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="1" t="n">
+      <c r="Q5" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q5" s="1" t="inlineStr">
+      <c r="R5" s="1" t="inlineStr">
         <is>
           <t>Potion_Party</t>
         </is>
       </c>
-      <c r="R5" s="1" t="inlineStr">
+      <c r="S5" s="1" t="inlineStr">
         <is>
           <t>Self_Experiment</t>
         </is>
       </c>
-      <c r="S5" s="1" t="n">
+      <c r="T5" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="T5" s="1" t="inlineStr">
+      <c r="U5" s="1" t="inlineStr">
         <is>
           <t>Even_Cook</t>
         </is>
       </c>
-      <c r="U5" s="1" t="n">
+      <c r="V5" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="V5" s="1" t="n">
+      <c r="W5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="W5" s="1" t="inlineStr">
+      <c r="X5" s="1" t="inlineStr">
         <is>
           <t>10층 보스. 초록 약품 플라스크를 3개씩 던짐 (떨어진 곳 쥐 기절)</t>
         </is>
@@ -992,83 +1013,86 @@
           <t>연구소장</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="1" t="n">
+        <v>2995003</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>boss_director</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="F6" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>Swing</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>Briefcase</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="J6" s="1" t="inlineStr">
         <is>
           <t>#d9786a</t>
         </is>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>2.8</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>2.8</v>
       </c>
       <c r="L6" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M6" s="1" t="n">
         <v>42.4</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="N6" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="O6" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="P6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="P6" s="1" t="n">
+      <c r="Q6" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q6" s="1" t="inlineStr">
+      <c r="R6" s="1" t="inlineStr">
         <is>
           <t>Paper_Storm</t>
         </is>
       </c>
-      <c r="R6" s="1" t="inlineStr">
+      <c r="S6" s="1" t="inlineStr">
         <is>
           <t>Board_Meeting</t>
         </is>
       </c>
-      <c r="S6" s="1" t="n">
+      <c r="T6" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="T6" s="1" t="inlineStr">
+      <c r="U6" s="1" t="inlineStr">
         <is>
           <t>Unbroken</t>
         </is>
       </c>
-      <c r="U6" s="1" t="n">
+      <c r="V6" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="V6" s="1" t="n">
+      <c r="W6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="W6" s="1" t="inlineStr">
+      <c r="X6" s="1" t="inlineStr">
         <is>
           <t>15층 보스. 주먹 휘두르기로 주변 쥐를 날림, 두 번에 한 번 경비원 호출</t>
         </is>
@@ -1083,83 +1107,86 @@
           <t>실험체 제로 (거대 메인쿤)</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="1" t="n">
+        <v>2995004</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>boss_zero</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Cat</t>
         </is>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="F7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>Pounce</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>Hairball</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="I7" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="J7" s="1" t="inlineStr">
         <is>
           <t>#e39a5a</t>
         </is>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>3.4</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>3.4</v>
       </c>
       <c r="L7" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M7" s="1" t="n">
         <v>50.5</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="N7" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="O7" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="P7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="P7" s="1" t="n">
+      <c r="Q7" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q7" s="1" t="inlineStr">
+      <c r="R7" s="1" t="inlineStr">
         <is>
           <t>Zoomies</t>
         </is>
       </c>
-      <c r="R7" s="1" t="inlineStr">
+      <c r="S7" s="1" t="inlineStr">
         <is>
           <t>Box_Fit</t>
         </is>
       </c>
-      <c r="S7" s="1" t="n">
+      <c r="T7" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="T7" s="1" t="inlineStr">
+      <c r="U7" s="1" t="inlineStr">
         <is>
           <t>Happy_Jump</t>
         </is>
       </c>
-      <c r="U7" s="1" t="n">
+      <c r="V7" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="V7" s="1" t="n">
+      <c r="W7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="W7" s="1" t="inlineStr">
+      <c r="X7" s="1" t="inlineStr">
         <is>
           <t>20층 보스. 거대 고양이: 덮치기 · 헤어볼 투척</t>
         </is>
@@ -1174,83 +1201,86 @@
           <t>대마법사 마녀 고양이</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="1" t="n">
+        <v>2995005</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>boss_witch</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Cat</t>
         </is>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="F8" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>Fireball</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>Pounce</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="I8" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="J8" s="1" t="inlineStr">
         <is>
           <t>#cdb4db</t>
         </is>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>3.4</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>3.4</v>
       </c>
       <c r="L8" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M8" s="1" t="n">
         <v>48.5</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="N8" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="N8" s="1" t="n">
+      <c r="O8" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="O8" s="1" t="n">
+      <c r="P8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="P8" s="1" t="n">
+      <c r="Q8" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q8" s="1" t="inlineStr">
+      <c r="R8" s="1" t="inlineStr">
         <is>
           <t>Meteor_Shower</t>
         </is>
       </c>
-      <c r="R8" s="1" t="inlineStr">
+      <c r="S8" s="1" t="inlineStr">
         <is>
           <t>Invis_Cloak</t>
         </is>
       </c>
-      <c r="S8" s="1" t="n">
+      <c r="T8" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="T8" s="1" t="inlineStr">
+      <c r="U8" s="1" t="inlineStr">
         <is>
           <t>Buttered_Cat</t>
         </is>
       </c>
-      <c r="U8" s="1" t="n">
+      <c r="V8" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="V8" s="1" t="n">
+      <c r="W8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="W8" s="1" t="inlineStr">
+      <c r="X8" s="1" t="inlineStr">
         <is>
           <t>25층 보스. 불덩이 5개 · 덮치기</t>
         </is>
@@ -1265,83 +1295,86 @@
           <t>우주 고양이 사령관</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="1" t="n">
+        <v>2995006</v>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>boss_commander</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Cat</t>
         </is>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="F9" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>Gravity</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>Pounce</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="I9" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="J9" s="1" t="inlineStr">
         <is>
           <t>#a9d3dc</t>
         </is>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>3.4</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>3.4</v>
       </c>
       <c r="L9" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M9" s="1" t="n">
         <v>32.4</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="N9" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="O9" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="P9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="P9" s="1" t="n">
+      <c r="Q9" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q9" s="1" t="inlineStr">
+      <c r="R9" s="1" t="inlineStr">
         <is>
           <t>Orbital_Laser</t>
         </is>
       </c>
-      <c r="R9" s="1" t="inlineStr">
+      <c r="S9" s="1" t="inlineStr">
         <is>
           <t>Black_Hole</t>
         </is>
       </c>
-      <c r="S9" s="1" t="n">
+      <c r="T9" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="T9" s="1" t="inlineStr">
+      <c r="U9" s="1" t="inlineStr">
         <is>
           <t>Maxwell_Drop</t>
         </is>
       </c>
-      <c r="U9" s="1" t="n">
+      <c r="V9" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="V9" s="1" t="n">
+      <c r="W9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="W9" s="1" t="inlineStr">
+      <c r="X9" s="1" t="inlineStr">
         <is>
           <t>30층 보스. 무중력 파동 (주변 쥐가 떠올랐다 떨어지며 기절) · 덮치기. 30층 뒤로는 5층 보스부터 다시 반복</t>
         </is>
@@ -1358,13 +1391,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1388,6 +1422,11 @@
           <t>대사</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>대사 키</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1410,6 +1449,11 @@
           <t>text</t>
         </is>
       </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>text_sk</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1430,6 +1474,11 @@
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -1450,6 +1499,9 @@
           <t>쥐는 한 마리도 못 지나간다!</t>
         </is>
       </c>
+      <c r="E4" s="1" t="n">
+        <v>3096001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1468,6 +1520,9 @@
           <t>흐으읍!</t>
         </is>
       </c>
+      <c r="E5" s="1" t="n">
+        <v>3096002</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1486,6 +1541,9 @@
           <t>짓밟아 주마!</t>
         </is>
       </c>
+      <c r="E6" s="1" t="n">
+        <v>3096003</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1504,6 +1562,9 @@
           <t>아야!</t>
         </is>
       </c>
+      <c r="E7" s="1" t="n">
+        <v>3096004</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1522,6 +1583,9 @@
           <t>이 녀석들이!</t>
         </is>
       </c>
+      <c r="E8" s="1" t="n">
+        <v>3096005</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1540,6 +1604,9 @@
           <t>끄악!</t>
         </is>
       </c>
+      <c r="E9" s="1" t="n">
+        <v>3096006</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1558,6 +1625,9 @@
           <t>비켜!</t>
         </is>
       </c>
+      <c r="E10" s="1" t="n">
+        <v>3096007</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1576,6 +1646,9 @@
           <t>기억해 두겠다아아~!</t>
         </is>
       </c>
+      <c r="E11" s="1" t="n">
+        <v>3096008</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1594,6 +1667,9 @@
           <t>퇴직금은?!</t>
         </is>
       </c>
+      <c r="E12" s="1" t="n">
+        <v>3096009</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1612,6 +1688,9 @@
           <t>으아아아~!</t>
         </is>
       </c>
+      <c r="E13" s="1" t="n">
+        <v>3096010</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1630,6 +1709,9 @@
           <t>내 실험체들이 탈출해?!</t>
         </is>
       </c>
+      <c r="E14" s="1" t="n">
+        <v>3096011</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1648,6 +1730,9 @@
           <t>실험체는 실험실로!</t>
         </is>
       </c>
+      <c r="E15" s="1" t="n">
+        <v>3096012</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1666,6 +1751,9 @@
           <t>이거나 먹어라!</t>
         </is>
       </c>
+      <c r="E16" s="1" t="n">
+        <v>3096013</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1684,6 +1772,9 @@
           <t>내 연구가!</t>
         </is>
       </c>
+      <c r="E17" s="1" t="n">
+        <v>3096014</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1702,6 +1793,9 @@
           <t>으윽, 시약이!</t>
         </is>
       </c>
+      <c r="E18" s="1" t="n">
+        <v>3096015</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1720,6 +1814,9 @@
           <t>감히!</t>
         </is>
       </c>
+      <c r="E19" s="1" t="n">
+        <v>3096016</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1738,6 +1835,9 @@
           <t>내 논문이이이~!</t>
         </is>
       </c>
+      <c r="E20" s="1" t="n">
+        <v>3096017</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1756,6 +1856,9 @@
           <t>실험 실패다아~!</t>
         </is>
       </c>
+      <c r="E21" s="1" t="n">
+        <v>3096018</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1774,6 +1877,9 @@
           <t>예산 삭감이다!!</t>
         </is>
       </c>
+      <c r="E22" s="1" t="n">
+        <v>3096019</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1792,6 +1898,9 @@
           <t>예산 삭감!</t>
         </is>
       </c>
+      <c r="E23" s="1" t="n">
+        <v>3096020</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1810,6 +1919,9 @@
           <t>해고다!!</t>
         </is>
       </c>
+      <c r="E24" s="1" t="n">
+        <v>3096021</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1828,6 +1940,9 @@
           <t>내 양복이!</t>
         </is>
       </c>
+      <c r="E25" s="1" t="n">
+        <v>3096023</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1846,6 +1961,9 @@
           <t>이건 감사 대상이야!</t>
         </is>
       </c>
+      <c r="E26" s="1" t="n">
+        <v>3096024</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1864,6 +1982,9 @@
           <t>아얏!</t>
         </is>
       </c>
+      <c r="E27" s="1" t="n">
+        <v>3096025</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1882,6 +2003,9 @@
           <t>퇴직금은?!</t>
         </is>
       </c>
+      <c r="E28" s="1" t="n">
+        <v>3096009</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1900,6 +2024,9 @@
           <t>기억해 두겠다아아~!</t>
         </is>
       </c>
+      <c r="E29" s="1" t="n">
+        <v>3096008</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1918,6 +2045,9 @@
           <t>냐아아아옹!!!</t>
         </is>
       </c>
+      <c r="E30" s="1" t="n">
+        <v>3096028</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1936,6 +2066,9 @@
           <t>냐아앙!!</t>
         </is>
       </c>
+      <c r="E31" s="1" t="n">
+        <v>3096029</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1954,6 +2087,9 @@
           <t>크르르…</t>
         </is>
       </c>
+      <c r="E32" s="1" t="n">
+        <v>3096030</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1972,6 +2108,9 @@
           <t>캑… 캑캑…</t>
         </is>
       </c>
+      <c r="E33" s="1" t="n">
+        <v>3096031</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1990,6 +2129,9 @@
           <t>우웨엑(헤어볼)!</t>
         </is>
       </c>
+      <c r="E34" s="1" t="n">
+        <v>3096032</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2008,6 +2150,9 @@
           <t>캬악!</t>
         </is>
       </c>
+      <c r="E35" s="1" t="n">
+        <v>3096033</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2026,6 +2171,9 @@
           <t>냐앙?!</t>
         </is>
       </c>
+      <c r="E36" s="1" t="n">
+        <v>3096034</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2044,6 +2192,9 @@
           <t>하악!</t>
         </is>
       </c>
+      <c r="E37" s="1" t="n">
+        <v>3096035</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2062,6 +2213,9 @@
           <t>냐아아아~!</t>
         </is>
       </c>
+      <c r="E38" s="1" t="n">
+        <v>3096036</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -2080,6 +2234,9 @@
           <t>냐옹…(기절)</t>
         </is>
       </c>
+      <c r="E39" s="1" t="n">
+        <v>3096037</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -2098,6 +2255,9 @@
           <t>냐브라카다브라!!</t>
         </is>
       </c>
+      <c r="E40" s="1" t="n">
+        <v>3096038</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -2116,6 +2276,9 @@
           <t>냐브라카다브라!</t>
         </is>
       </c>
+      <c r="E41" s="1" t="n">
+        <v>3096039</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -2134,6 +2297,9 @@
           <t>불타라 냥!</t>
         </is>
       </c>
+      <c r="E42" s="1" t="n">
+        <v>3096040</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -2152,6 +2318,9 @@
           <t>냐아앙!!</t>
         </is>
       </c>
+      <c r="E43" s="1" t="n">
+        <v>3096029</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -2170,6 +2339,9 @@
           <t>내 모자가!</t>
         </is>
       </c>
+      <c r="E44" s="1" t="n">
+        <v>3096042</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -2188,6 +2360,9 @@
           <t>캬악!</t>
         </is>
       </c>
+      <c r="E45" s="1" t="n">
+        <v>3096033</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -2206,6 +2381,9 @@
           <t>주문이 꼬였다냥!</t>
         </is>
       </c>
+      <c r="E46" s="1" t="n">
+        <v>3096044</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -2224,6 +2402,9 @@
           <t>마법이 풀렸다냐아~!</t>
         </is>
       </c>
+      <c r="E47" s="1" t="n">
+        <v>3096045</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -2242,6 +2423,9 @@
           <t>냐아아아~!</t>
         </is>
       </c>
+      <c r="E48" s="1" t="n">
+        <v>3096036</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -2260,6 +2444,9 @@
           <t>이 연구소는 우주 냥국이 접수한다!</t>
         </is>
       </c>
+      <c r="E49" s="1" t="n">
+        <v>3096047</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -2278,6 +2465,9 @@
           <t>중력 해제 냥!</t>
         </is>
       </c>
+      <c r="E50" s="1" t="n">
+        <v>3096048</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -2296,6 +2486,9 @@
           <t>둥실둥실 냥~</t>
         </is>
       </c>
+      <c r="E51" s="1" t="n">
+        <v>3096049</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -2314,6 +2507,9 @@
           <t>냐아앙!!</t>
         </is>
       </c>
+      <c r="E52" s="1" t="n">
+        <v>3096029</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -2332,6 +2528,9 @@
           <t>헬멧에 금이!</t>
         </is>
       </c>
+      <c r="E53" s="1" t="n">
+        <v>3096051</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -2350,6 +2549,9 @@
           <t>캬악!</t>
         </is>
       </c>
+      <c r="E54" s="1" t="n">
+        <v>3096033</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -2368,6 +2570,9 @@
           <t>지구 쥐 주제에!</t>
         </is>
       </c>
+      <c r="E55" s="1" t="n">
+        <v>3096053</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -2386,6 +2591,9 @@
           <t>우주로 돌아간다냐아~!</t>
         </is>
       </c>
+      <c r="E56" s="1" t="n">
+        <v>3096054</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -2404,6 +2612,9 @@
           <t>냐아아아~!</t>
         </is>
       </c>
+      <c r="E57" s="1" t="n">
+        <v>3096036</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -2422,6 +2633,9 @@
           <t>실험은 폭발이다아아!!</t>
         </is>
       </c>
+      <c r="E58" s="1" t="n">
+        <v>3096059</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -2440,6 +2654,9 @@
           <t>이번엔 이걸 섞어볼까~?</t>
         </is>
       </c>
+      <c r="E59" s="1" t="n">
+        <v>3096060</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -2458,6 +2675,9 @@
           <t>내 몸으로 직접 실험한다!!</t>
         </is>
       </c>
+      <c r="E60" s="1" t="n">
+        <v>3096061</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -2476,6 +2696,9 @@
           <t>퉁! 퉁! 퉁! 사후르!!</t>
         </is>
       </c>
+      <c r="E61" s="1" t="n">
+        <v>3096074</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -2494,6 +2717,9 @@
           <t>사후르 시간이다!!</t>
         </is>
       </c>
+      <c r="E62" s="1" t="n">
+        <v>3096075</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -2512,6 +2738,9 @@
           <t>퉁퉁퉁퉁퉁퉁퉁퉁퉁 사후르!</t>
         </is>
       </c>
+      <c r="E63" s="1" t="n">
+        <v>3096076</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -2530,6 +2759,9 @@
           <t>진압봉 맛 좀 봐라!</t>
         </is>
       </c>
+      <c r="E64" s="1" t="n">
+        <v>3096077</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -2548,6 +2780,9 @@
           <t>이븐하게 익혀 드릴게요~</t>
         </is>
       </c>
+      <c r="E65" s="1" t="n">
+        <v>3096078</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -2566,6 +2801,9 @@
           <t>익힘 정도가 아주 이븐하네요!</t>
         </is>
       </c>
+      <c r="E66" s="1" t="n">
+        <v>3096079</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -2584,6 +2822,9 @@
           <t>쥐 요리는 굽기가 생명이지!</t>
         </is>
       </c>
+      <c r="E67" s="1" t="n">
+        <v>3096080</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -2602,6 +2843,9 @@
           <t>숨 참아 봐~ 독가스다!</t>
         </is>
       </c>
+      <c r="E68" s="1" t="n">
+        <v>3096081</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -2620,6 +2864,9 @@
           <t>중요한 건 꺾이지 않는 마음!!</t>
         </is>
       </c>
+      <c r="E69" s="1" t="n">
+        <v>3096082</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -2638,6 +2885,9 @@
           <t>중꺾마다!!</t>
         </is>
       </c>
+      <c r="E70" s="1" t="n">
+        <v>3096083</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -2656,6 +2906,9 @@
           <t>이 정도로 꺾일 소장이 아니다!</t>
         </is>
       </c>
+      <c r="E71" s="1" t="n">
+        <v>3096084</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -2674,6 +2927,9 @@
           <t>서류는 던지라고 있는 거야!</t>
         </is>
       </c>
+      <c r="E72" s="1" t="n">
+        <v>3096085</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -2692,6 +2948,9 @@
           <t>해피해피해피~!</t>
         </is>
       </c>
+      <c r="E73" s="1" t="n">
+        <v>3096086</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -2710,6 +2969,9 @@
           <t>(통 통 통)</t>
         </is>
       </c>
+      <c r="E74" s="1" t="n">
+        <v>3096087</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -2728,6 +2990,9 @@
           <t>냥피냥피냥피!</t>
         </is>
       </c>
+      <c r="E75" s="1" t="n">
+        <v>3096088</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -2746,6 +3011,9 @@
           <t>무한동력이다냥!</t>
         </is>
       </c>
+      <c r="E76" s="1" t="n">
+        <v>3096089</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -2764,6 +3032,9 @@
           <t>식빵이 먼저냐, 고양이가 먼저냐!</t>
         </is>
       </c>
+      <c r="E77" s="1" t="n">
+        <v>3096090</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -2782,6 +3053,9 @@
           <t>버터 바른 고양이 출동~!</t>
         </is>
       </c>
+      <c r="E78" s="1" t="n">
+        <v>3096091</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -2800,6 +3074,9 @@
           <t>맥스웰 부대, 강하.</t>
         </is>
       </c>
+      <c r="E79" s="1" t="n">
+        <v>3096092</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -2818,6 +3095,9 @@
           <t>빙글빙글 맥스웰 투하!</t>
         </is>
       </c>
+      <c r="E80" s="1" t="n">
+        <v>3096093</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -2836,6 +3116,9 @@
           <t>(맥스웰 테마 흥얼흥얼)</t>
         </is>
       </c>
+      <c r="E81" s="1" t="n">
+        <v>3096094</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -2854,6 +3137,9 @@
           <t>무야호~!!!</t>
         </is>
       </c>
+      <c r="E82" s="1" t="n">
+        <v>3096095</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -2872,6 +3158,9 @@
           <t>그만큼 신나신다는 거지!!</t>
         </is>
       </c>
+      <c r="E83" s="1" t="n">
+        <v>3096096</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -2890,6 +3179,9 @@
           <t>관짝 들어갑니다~ (빠밤 빠밤)</t>
         </is>
       </c>
+      <c r="E84" s="1" t="n">
+        <v>3096097</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -2908,6 +3200,9 @@
           <t>펑?! ...오히려 좋아!!</t>
         </is>
       </c>
+      <c r="E85" s="1" t="n">
+        <v>3096098</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -2926,6 +3221,9 @@
           <t>실험 실패? 오히려 좋아!!</t>
         </is>
       </c>
+      <c r="E86" s="1" t="n">
+        <v>3096099</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -2944,6 +3242,9 @@
           <t>이 층, 전액 현금 매입이다!!</t>
         </is>
       </c>
+      <c r="E87" s="1" t="n">
+        <v>3096100</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -2962,6 +3263,9 @@
           <t>긴급 회의!! 누가 임포스터지?</t>
         </is>
       </c>
+      <c r="E88" s="1" t="n">
+        <v>3096101</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -2980,6 +3284,9 @@
           <t>쥐가 임포스터다!! 투표해!!</t>
         </is>
       </c>
+      <c r="E89" s="1" t="n">
+        <v>3096102</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -2998,6 +3305,9 @@
           <t>(한강 위를 걷는 고양이)</t>
         </is>
       </c>
+      <c r="E90" s="1" t="n">
+        <v>3096103</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -3016,6 +3326,9 @@
           <t>꽁냥꽁냥~!!</t>
         </is>
       </c>
+      <c r="E91" s="1" t="n">
+        <v>3096104</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -3034,6 +3347,9 @@
           <t>(엉엉엉엉) 바나나...</t>
         </is>
       </c>
+      <c r="E92" s="1" t="n">
+        <v>3096105</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -3052,6 +3368,9 @@
           <t>트랄랄레로 트랄랄라~!</t>
         </is>
       </c>
+      <c r="E93" s="1" t="n">
+        <v>3096106</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -3070,6 +3389,9 @@
           <t>상어 신발 신고 트랄랄라~ 냥!</t>
         </is>
       </c>
+      <c r="E94" s="1" t="n">
+        <v>3096107</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -3088,6 +3410,9 @@
           <t>머리를 바꿔 주겠다냥!</t>
         </is>
       </c>
+      <c r="E95" s="1" t="n">
+        <v>3096108</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -3106,6 +3431,9 @@
           <t>우리는 답을 찾을 것이다. 늘 그랬듯이.</t>
         </is>
       </c>
+      <c r="E96" s="1" t="n">
+        <v>3096109</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -3124,6 +3452,9 @@
           <t>No... it's necessary.</t>
         </is>
       </c>
+      <c r="E97" s="1" t="n">
+        <v>3096110</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -3141,6 +3472,9 @@
         <is>
           <t>눈에서 레이저 나간다냥.</t>
         </is>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>3096111</v>
       </c>
     </row>
   </sheetData>
@@ -3154,7 +3488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3164,7 +3498,8 @@
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3210,7 +3545,17 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>화면 이름 키</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>전용 대사</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>전용 대사 키</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3602,17 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
+          <t>atk_name_sk</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
           <t>line</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>line_sk</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3659,17 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3704,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr"/>
+      <c r="I4" s="1" t="n"/>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -3372,7 +3739,11 @@
           <t>내려찍기</t>
         </is>
       </c>
-      <c r="I5" s="1" t="inlineStr"/>
+      <c r="I5" s="1" t="n">
+        <v>3100001</v>
+      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -3405,7 +3776,11 @@
           <t>덮치기</t>
         </is>
       </c>
-      <c r="I6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="n">
+        <v>3100002</v>
+      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -3438,7 +3813,11 @@
           <t>플라스크 투척</t>
         </is>
       </c>
-      <c r="I7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="n">
+        <v>3100003</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -3471,7 +3850,11 @@
           <t>헤어볼</t>
         </is>
       </c>
-      <c r="I8" s="1" t="inlineStr"/>
+      <c r="I8" s="1" t="n">
+        <v>3100004</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -3504,7 +3887,11 @@
           <t>불덩이</t>
         </is>
       </c>
-      <c r="I9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="n">
+        <v>3100005</v>
+      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -3537,7 +3924,11 @@
           <t>휘두르기</t>
         </is>
       </c>
-      <c r="I10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="n">
+        <v>3100006</v>
+      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -3570,7 +3961,11 @@
           <t>무중력 파동</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="n">
+        <v>3100007</v>
+      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -3603,7 +3998,11 @@
           <t>무야호~!! 3단 점프</t>
         </is>
       </c>
-      <c r="I12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="n">
+        <v>3100008</v>
+      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3636,7 +4035,11 @@
           <t>관짝소년단</t>
         </is>
       </c>
-      <c r="I13" s="1" t="inlineStr"/>
+      <c r="I13" s="1" t="n">
+        <v>3100009</v>
+      </c>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -3669,7 +4072,11 @@
           <t>약품 대방출 파티</t>
         </is>
       </c>
-      <c r="I14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="n">
+        <v>3100010</v>
+      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -3702,7 +4109,11 @@
           <t>오히려 좋아!!</t>
         </is>
       </c>
-      <c r="I15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="n">
+        <v>3100011</v>
+      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -3735,7 +4146,11 @@
           <t>전액 현금 매입</t>
         </is>
       </c>
-      <c r="I16" s="1" t="inlineStr"/>
+      <c r="I16" s="1" t="n">
+        <v>3100012</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -3768,7 +4183,11 @@
           <t>긴급 비상 회의!!</t>
         </is>
       </c>
-      <c r="I17" s="1" t="inlineStr"/>
+      <c r="I17" s="1" t="n">
+        <v>3100013</v>
+      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -3801,10 +4220,16 @@
           <t>꽁꽁 얼어붙은 한강</t>
         </is>
       </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="I18" s="1" t="n">
+        <v>3100014</v>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
         <is>
           <t>꽁꽁 얼어붙은 한강 위로 고양이가 걸어다닙니다</t>
         </is>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>3200001</v>
       </c>
     </row>
     <row r="19">
@@ -3838,7 +4263,11 @@
           <t>바나나 고양이 소환</t>
         </is>
       </c>
-      <c r="I19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="n">
+        <v>3100015</v>
+      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -3871,7 +4300,11 @@
           <t>트랄랄레로 트랄랄라</t>
         </is>
       </c>
-      <c r="I20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="n">
+        <v>3100016</v>
+      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -3904,7 +4337,11 @@
           <t>발레리나 카푸치나</t>
         </is>
       </c>
-      <c r="I21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="n">
+        <v>3100017</v>
+      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -3937,10 +4374,16 @@
           <t>홈랜더 눈 레이저</t>
         </is>
       </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="I22" s="1" t="n">
+        <v>3100018</v>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
         <is>
           <t>난 너희들보다 강하고, 똑똑하고, 더 낫다. 난 더 낫다고!</t>
         </is>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>3200002</v>
       </c>
     </row>
     <row r="23">
@@ -3974,7 +4417,11 @@
           <t>STAY</t>
         </is>
       </c>
-      <c r="I23" s="1" t="inlineStr"/>
+      <c r="I23" s="1" t="n">
+        <v>3100029</v>
+      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -4007,7 +4454,11 @@
           <t>진압봉 휘두르기</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr"/>
+      <c r="I24" s="1" t="n">
+        <v>3100019</v>
+      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4040,7 +4491,11 @@
           <t>독가스 구름</t>
         </is>
       </c>
-      <c r="I25" s="1" t="inlineStr"/>
+      <c r="I25" s="1" t="n">
+        <v>3100020</v>
+      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -4073,7 +4528,11 @@
           <t>서류 가방 던지기</t>
         </is>
       </c>
-      <c r="I26" s="1" t="inlineStr"/>
+      <c r="I26" s="1" t="n">
+        <v>3100021</v>
+      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -4106,7 +4565,11 @@
           <t>퉁퉁퉁 사후르</t>
         </is>
       </c>
-      <c r="I27" s="1" t="inlineStr"/>
+      <c r="I27" s="1" t="n">
+        <v>3100022</v>
+      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -4139,7 +4602,11 @@
           <t>이븐하게 익혀드릴게요</t>
         </is>
       </c>
-      <c r="I28" s="1" t="inlineStr"/>
+      <c r="I28" s="1" t="n">
+        <v>3100023</v>
+      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -4172,10 +4639,16 @@
           <t>중요한 건 꺾이지 않는 마음</t>
         </is>
       </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="I29" s="1" t="n">
+        <v>3100024</v>
+      </c>
+      <c r="J29" s="1" t="inlineStr">
         <is>
           <t>중요한 건 꺾이지 않는 마음!!</t>
         </is>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>3200003</v>
       </c>
     </row>
     <row r="30">
@@ -4209,7 +4682,11 @@
           <t>해피해피해피</t>
         </is>
       </c>
-      <c r="I30" s="1" t="inlineStr"/>
+      <c r="I30" s="1" t="n">
+        <v>3100025</v>
+      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -4242,7 +4719,11 @@
           <t>무한동력 버터 고양이</t>
         </is>
       </c>
-      <c r="I31" s="1" t="inlineStr"/>
+      <c r="I31" s="1" t="n">
+        <v>3100026</v>
+      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -4275,7 +4756,11 @@
           <t>맥스웰 고양이 낙하</t>
         </is>
       </c>
-      <c r="I32" s="1" t="inlineStr"/>
+      <c r="I32" s="1" t="n">
+        <v>3100027</v>
+      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -4308,10 +4793,16 @@
           <t>투명 망토</t>
         </is>
       </c>
-      <c r="I33" s="1" t="inlineStr">
+      <c r="I33" s="1" t="n">
+        <v>3100028</v>
+      </c>
+      <c r="J33" s="1" t="inlineStr">
         <is>
           <t>나는 나쁜 짓을 할 것을 엄숙히 맹세한다냥!</t>
         </is>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>3200004</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="X8" s="1" t="inlineStr">
         <is>
-          <t>25층 보스. 불덩이 5개 · 덮치기</t>
+          <t>(미사용 2026-10-19: 16~30층 고양이 연구소로 교체, 테스트 패널로만) 25층 보스. 불덩이 5개 · 덮치기</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
@@ -1376,7 +1376,1605 @@
       </c>
       <c r="X9" s="1" t="inlineStr">
         <is>
-          <t>30층 보스. 무중력 파동 (주변 쥐가 떠올랐다 떨어지며 기절) · 덮치기. 30층 뒤로는 5층 보스부터 다시 반복</t>
+          <t>(미사용 2026-10-19: 16~30층 고양이 연구소로 교체, 테스트 패널로만) 30층 보스. 무중력 파동 (주변 쥐가 떠올랐다 떨어지며 기절) · 덮치기. 30층 뒤로는 5층 보스부터 다시 반복</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>95007</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>해피 고양이</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>2995007</v>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>boss_happy</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>#f3efe6</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R10" s="1" t="inlineStr">
+        <is>
+          <t>Happy_Rain</t>
+        </is>
+      </c>
+      <c r="S10" s="1" t="inlineStr">
+        <is>
+          <t>Huh_Cat</t>
+        </is>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U10" s="1" t="inlineStr">
+        <is>
+          <t>Chipi_Chapa</t>
+        </is>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X10" s="1" t="inlineStr">
+        <is>
+          <t>25층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Chipi_Chapa · Happy_Rain · Huh_Cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>95008</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>팝 고양이</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>2995008</v>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>boss_pop</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>#f0a65a</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R11" s="1" t="inlineStr">
+        <is>
+          <t>Pop_Clicker</t>
+        </is>
+      </c>
+      <c r="S11" s="1" t="inlineStr">
+        <is>
+          <t>Vibing_Cat</t>
+        </is>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U11" s="1" t="inlineStr">
+        <is>
+          <t>Pop_Pop</t>
+        </is>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X11" s="1" t="inlineStr">
+        <is>
+          <t>30층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Pop_Pop · Pop_Clicker · Vibing_Cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>95009</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>원시인 우가</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>2995009</v>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>boss_caveman</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>Rock_Throw</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>#b7804a</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R12" s="1" t="inlineStr">
+        <is>
+          <t>Return_To_Monke</t>
+        </is>
+      </c>
+      <c r="S12" s="1" t="inlineStr">
+        <is>
+          <t>Extinction</t>
+        </is>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U12" s="1" t="inlineStr">
+        <is>
+          <t>Fire_Discovery</t>
+        </is>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X12" s="1" t="inlineStr">
+        <is>
+          <t>35층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Fire_Discovery · Return_To_Monke · Extinction</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>95010</v>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>랩터 사육사</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>2995010</v>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>boss_keeper</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>#6f8a5a</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R13" s="1" t="inlineStr">
+        <is>
+          <t>Clever_Girl</t>
+        </is>
+      </c>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t>Tranq_Dart</t>
+        </is>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U13" s="1" t="inlineStr">
+        <is>
+          <t>Hold_Up</t>
+        </is>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X13" s="1" t="inlineStr">
+        <is>
+          <t>40층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Hold_Up · Clever_Girl · Tranq_Dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>95011</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>공룡탈 알바</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>2995011</v>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>boss_dino</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>#7cb86a</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R14" s="1" t="inlineStr">
+        <is>
+          <t>Tiny_Arms</t>
+        </is>
+      </c>
+      <c r="S14" s="1" t="inlineStr">
+        <is>
+          <t>Deflate</t>
+        </is>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U14" s="1" t="inlineStr">
+        <is>
+          <t>Trex_Dance</t>
+        </is>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X14" s="1" t="inlineStr">
+        <is>
+          <t>45층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Trex_Dance · Tiny_Arms · Deflate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>95012</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>야가다 김씨</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>2995012</v>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>boss_kim</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>#e0b23a</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R15" s="1" t="inlineStr">
+        <is>
+          <t>Concrete</t>
+        </is>
+      </c>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>Joa_Ssu</t>
+        </is>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U15" s="1" t="inlineStr">
+        <is>
+          <t>Excavator</t>
+        </is>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X15" s="1" t="inlineStr">
+        <is>
+          <t>50층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Excavator · Concrete · Joa_Ssu</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>95013</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>노조 고양이</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>2995013</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>boss_union</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>#c9564a</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R16" s="1" t="inlineStr">
+        <is>
+          <t>Churu_Raise</t>
+        </is>
+      </c>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t>Lie_Down</t>
+        </is>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U16" s="1" t="inlineStr">
+        <is>
+          <t>Picket</t>
+        </is>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X16" s="1" t="inlineStr">
+        <is>
+          <t>55층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Picket · Churu_Raise · Lie_Down</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>95014</v>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>함바집 아줌마</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>2995014</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>boss_hamba</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>Rice_Bowl</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>#e57b7b</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R17" s="1" t="inlineStr">
+        <is>
+          <t>Did_You_Eat</t>
+        </is>
+      </c>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t>Ladle_Spin</t>
+        </is>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U17" s="1" t="inlineStr">
+        <is>
+          <t>Gobong</t>
+        </is>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W17" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X17" s="1" t="inlineStr">
+        <is>
+          <t>60층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Gobong · Did_You_Eat · Ladle_Spin</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>95015</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>인어 고양이</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>2995015</v>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>boss_mermaid</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>Bubble_Shot</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>#6cc4c0</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R18" s="1" t="inlineStr">
+        <is>
+          <t>Tidal_Wave</t>
+        </is>
+      </c>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>Fish_Slap</t>
+        </is>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U18" s="1" t="inlineStr">
+        <is>
+          <t>Under_The_Sea</t>
+        </is>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X18" s="1" t="inlineStr">
+        <is>
+          <t>65층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Under_The_Sea · Tidal_Wave · Fish_Slap</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>95016</v>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>잠수복 고양이</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>2995016</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>boss_diver</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>#c89b4a</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R19" s="1" t="inlineStr">
+        <is>
+          <t>Sonar_Ping</t>
+        </is>
+      </c>
+      <c r="S19" s="1" t="inlineStr">
+        <is>
+          <t>Octo_Ink</t>
+        </is>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U19" s="1" t="inlineStr">
+        <is>
+          <t>Anchor_Drop</t>
+        </is>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W19" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X19" s="1" t="inlineStr">
+        <is>
+          <t>70층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Anchor_Drop · Sonar_Ping · Octo_Ink</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>95017</v>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>상어 고양이</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>2995017</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>boss_shark</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>#7f97ad</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R20" s="1" t="inlineStr">
+        <is>
+          <t>Jaws_Dash</t>
+        </is>
+      </c>
+      <c r="S20" s="1" t="inlineStr">
+        <is>
+          <t>Sharknado</t>
+        </is>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U20" s="1" t="inlineStr">
+        <is>
+          <t>Baby_Shark</t>
+        </is>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W20" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X20" s="1" t="inlineStr">
+        <is>
+          <t>75층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Baby_Shark · Jaws_Dash · Sharknado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>95018</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>포탑 고양이</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>2995018</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>boss_turret</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>#7d8a4e</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R21" s="1" t="inlineStr">
+        <is>
+          <t>Barrage</t>
+        </is>
+      </c>
+      <c r="S21" s="1" t="inlineStr">
+        <is>
+          <t>No_Scope</t>
+        </is>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U21" s="1" t="inlineStr">
+        <is>
+          <t>Wrong_Way</t>
+        </is>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W21" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X21" s="1" t="inlineStr">
+        <is>
+          <t>80층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Wrong_Way · Barrage · No_Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>95019</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>라이언 이병 고양이</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>2995019</v>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>boss_ryan</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>#d9a441</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R22" s="1" t="inlineStr">
+        <is>
+          <t>Circle_Of_Life</t>
+        </is>
+      </c>
+      <c r="S22" s="1" t="inlineStr">
+        <is>
+          <t>Supply_Drop</t>
+        </is>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U22" s="1" t="inlineStr">
+        <is>
+          <t>Lion_Roar</t>
+        </is>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W22" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X22" s="1" t="inlineStr">
+        <is>
+          <t>85층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Lion_Roar · Circle_Of_Life · Supply_Drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>95020</v>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>총통 고양이</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>2995020</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>boss_fuhrer</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>#7a7a7a</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R23" s="1" t="inlineStr">
+        <is>
+          <t>Bunker_Rant</t>
+        </is>
+      </c>
+      <c r="S23" s="1" t="inlineStr">
+        <is>
+          <t>Map_Slam</t>
+        </is>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U23" s="1" t="inlineStr">
+        <is>
+          <t>Pencil_Throw</t>
+        </is>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W23" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X23" s="1" t="inlineStr">
+        <is>
+          <t>90층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Pencil_Throw · Bunker_Rant · Map_Slam</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>95021</v>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>빨간 우주복</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>2995021</v>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>boss_red</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>#d43b3b</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R24" s="1" t="inlineStr">
+        <is>
+          <t>Sus</t>
+        </is>
+      </c>
+      <c r="S24" s="1" t="inlineStr">
+        <is>
+          <t>Lights_Out</t>
+        </is>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U24" s="1" t="inlineStr">
+        <is>
+          <t>Vent</t>
+        </is>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W24" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X24" s="1" t="inlineStr">
+        <is>
+          <t>94층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Vent · Sus · Lights_Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>95022</v>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>레이저 눈 고양이</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>2995022</v>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>boss_lasercat</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>#6b4ac8</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R25" s="1" t="inlineStr">
+        <is>
+          <t>OIIA</t>
+        </is>
+      </c>
+      <c r="S25" s="1" t="inlineStr">
+        <is>
+          <t>Galaxy_Bang</t>
+        </is>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U25" s="1" t="inlineStr">
+        <is>
+          <t>Laser_Eyes</t>
+        </is>
+      </c>
+      <c r="V25" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X25" s="1" t="inlineStr">
+        <is>
+          <t>97층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Laser_Eyes · OIIA · Galaxy_Bang</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>95023</v>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>우주 사령관 그럼피</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>2995023</v>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>boss_grumpy</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>#5a6fa8</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R26" s="1" t="inlineStr">
+        <is>
+          <t>Had_Fun_Once</t>
+        </is>
+      </c>
+      <c r="S26" s="1" t="inlineStr">
+        <is>
+          <t>Moon_Drop</t>
+        </is>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U26" s="1" t="inlineStr">
+        <is>
+          <t>No_Cat</t>
+        </is>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W26" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X26" s="1" t="inlineStr">
+        <is>
+          <t>100층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type No_Cat · Had_Fun_Once · Moon_Drop</t>
         </is>
       </c>
     </row>
@@ -1391,7 +2989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3477,6 +5075,3219 @@
         <v>3096111</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>96201</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>95007</v>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
+        <is>
+          <t>해피해피해피~!!</t>
+        </is>
+      </c>
+      <c r="E99" s="1" t="n">
+        <v>3096201</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>96202</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>95007</v>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>냥!</t>
+        </is>
+      </c>
+      <c r="E100" s="1" t="n">
+        <v>3096202</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>96203</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>95007</v>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr">
+        <is>
+          <t>통통!</t>
+        </is>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>3096203</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>96204</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>95007</v>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t>냥?!</t>
+        </is>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>3096204</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>96205</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>95007</v>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr">
+        <is>
+          <t>안 해피해!</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>3096205</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>96206</v>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>95007</v>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>해피… 해피…</t>
+        </is>
+      </c>
+      <c r="E104" s="1" t="n">
+        <v>3096206</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>96207</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>95007</v>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>냐아아~</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>3096207</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>96208</v>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>95007</v>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr">
+        <is>
+          <t>다 같이 해피~!</t>
+        </is>
+      </c>
+      <c r="E106" s="1" t="n">
+        <v>3096208</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>96209</v>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>95007</v>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t>치피치피~</t>
+        </is>
+      </c>
+      <c r="E107" s="1" t="n">
+        <v>3096209</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>96210</v>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>95008</v>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>팝!!</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="n">
+        <v>3096210</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>96211</v>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>95008</v>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
+        <is>
+          <t>팝!</t>
+        </is>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>3096211</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>96212</v>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>95008</v>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>뻐끔!</t>
+        </is>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>3096212</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>96213</v>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>95008</v>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="inlineStr">
+        <is>
+          <t>팝?!</t>
+        </is>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>3096213</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>96214</v>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>95008</v>
+      </c>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="inlineStr">
+        <is>
+          <t>캬악!</t>
+        </is>
+      </c>
+      <c r="E112" s="1" t="n">
+        <v>3096033</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>96215</v>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>95008</v>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="inlineStr">
+        <is>
+          <t>팝… 팝…</t>
+        </is>
+      </c>
+      <c r="E113" s="1" t="n">
+        <v>3096215</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>96216</v>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>95008</v>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t>클릭 수가…!</t>
+        </is>
+      </c>
+      <c r="E114" s="1" t="n">
+        <v>3096216</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>96217</v>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>95008</v>
+      </c>
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="inlineStr">
+        <is>
+          <t>전 세계 클릭 1등이다!</t>
+        </is>
+      </c>
+      <c r="E115" s="1" t="n">
+        <v>3096217</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>96218</v>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>95008</v>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t>팝팝팝!</t>
+        </is>
+      </c>
+      <c r="E116" s="1" t="n">
+        <v>3096218</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>96219</v>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>95009</v>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="inlineStr">
+        <is>
+          <t>우가! 쥐! 사냥!</t>
+        </is>
+      </c>
+      <c r="E117" s="1" t="n">
+        <v>3096219</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>96220</v>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>95009</v>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t>우가!</t>
+        </is>
+      </c>
+      <c r="E118" s="1" t="n">
+        <v>3096220</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>96221</v>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>95009</v>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="inlineStr">
+        <is>
+          <t>부가!</t>
+        </is>
+      </c>
+      <c r="E119" s="1" t="n">
+        <v>3096221</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>96222</v>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>95009</v>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t>우우?!</t>
+        </is>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>3096222</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>96223</v>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>95009</v>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
+          <t>아파 우가!</t>
+        </is>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>3096223</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>96224</v>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>95009</v>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t>불… 무서워…</t>
+        </is>
+      </c>
+      <c r="E122" s="1" t="n">
+        <v>3096224</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>96225</v>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>95009</v>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr">
+        <is>
+          <t>우가아아~</t>
+        </is>
+      </c>
+      <c r="E123" s="1" t="n">
+        <v>3096225</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>96226</v>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>95009</v>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr">
+        <is>
+          <t>원숭이로 돌아간다!</t>
+        </is>
+      </c>
+      <c r="E124" s="1" t="n">
+        <v>3096226</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>96227</v>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>95009</v>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr">
+        <is>
+          <t>이건… 불?!</t>
+        </is>
+      </c>
+      <c r="E125" s="1" t="n">
+        <v>3096227</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>96228</v>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>95010</v>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>내 랩터들 건드리지 마.</t>
+        </is>
+      </c>
+      <c r="E126" s="1" t="n">
+        <v>3096228</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>96229</v>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>95010</v>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>물러서!</t>
+        </is>
+      </c>
+      <c r="E127" s="1" t="n">
+        <v>3096229</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>96230</v>
+      </c>
+      <c r="B128" s="1" t="n">
+        <v>95010</v>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t>조심해!</t>
+        </is>
+      </c>
+      <c r="E128" s="1" t="n">
+        <v>3096230</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>96231</v>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>95010</v>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="inlineStr">
+        <is>
+          <t>으윽!</t>
+        </is>
+      </c>
+      <c r="E129" s="1" t="n">
+        <v>3096231</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>96232</v>
+      </c>
+      <c r="B130" s="1" t="n">
+        <v>95010</v>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t>이건 계획에 없었어!</t>
+        </is>
+      </c>
+      <c r="E130" s="1" t="n">
+        <v>3096232</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>96233</v>
+      </c>
+      <c r="B131" s="1" t="n">
+        <v>95010</v>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>영리한… 녀석들…</t>
+        </is>
+      </c>
+      <c r="E131" s="1" t="n">
+        <v>3096233</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>96234</v>
+      </c>
+      <c r="B132" s="1" t="n">
+        <v>95010</v>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>후퇴다!</t>
+        </is>
+      </c>
+      <c r="E132" s="1" t="n">
+        <v>3096234</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>96235</v>
+      </c>
+      <c r="B133" s="1" t="n">
+        <v>95010</v>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="inlineStr">
+        <is>
+          <t>블루, 가!</t>
+        </is>
+      </c>
+      <c r="E133" s="1" t="n">
+        <v>3096235</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>96236</v>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>95010</v>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t>진정해, 진정…</t>
+        </is>
+      </c>
+      <c r="E134" s="1" t="n">
+        <v>3096236</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>96237</v>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>95011</v>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="inlineStr">
+        <is>
+          <t>어서 오세요~ 공룡 체험관입니다!</t>
+        </is>
+      </c>
+      <c r="E135" s="1" t="n">
+        <v>3096237</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>96238</v>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>95011</v>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="inlineStr">
+        <is>
+          <t>크아앙!</t>
+        </is>
+      </c>
+      <c r="E136" s="1" t="n">
+        <v>3096238</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>96239</v>
+      </c>
+      <c r="B137" s="1" t="n">
+        <v>95011</v>
+      </c>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="inlineStr">
+        <is>
+          <t>둠칫!</t>
+        </is>
+      </c>
+      <c r="E137" s="1" t="n">
+        <v>3096239</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>96240</v>
+      </c>
+      <c r="B138" s="1" t="n">
+        <v>95011</v>
+      </c>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D138" s="1" t="inlineStr">
+        <is>
+          <t>바람 빠져요!</t>
+        </is>
+      </c>
+      <c r="E138" s="1" t="n">
+        <v>3096240</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>96241</v>
+      </c>
+      <c r="B139" s="1" t="n">
+        <v>95011</v>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="inlineStr">
+        <is>
+          <t>시급이 얼만데!</t>
+        </is>
+      </c>
+      <c r="E139" s="1" t="n">
+        <v>3096241</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>96242</v>
+      </c>
+      <c r="B140" s="1" t="n">
+        <v>95011</v>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="inlineStr">
+        <is>
+          <t>퇴근할래요…</t>
+        </is>
+      </c>
+      <c r="E140" s="1" t="n">
+        <v>3096242</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>96243</v>
+      </c>
+      <c r="B141" s="1" t="n">
+        <v>95011</v>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="inlineStr">
+        <is>
+          <t>푸쉬이이~</t>
+        </is>
+      </c>
+      <c r="E141" s="1" t="n">
+        <v>3096243</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>96244</v>
+      </c>
+      <c r="B142" s="1" t="n">
+        <v>95011</v>
+      </c>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="inlineStr">
+        <is>
+          <t>팔이 안 닿아!!</t>
+        </is>
+      </c>
+      <c r="E142" s="1" t="n">
+        <v>3096244</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>96245</v>
+      </c>
+      <c r="B143" s="1" t="n">
+        <v>95011</v>
+      </c>
+      <c r="C143" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D143" s="1" t="inlineStr">
+        <is>
+          <t>둠칫둠칫~</t>
+        </is>
+      </c>
+      <c r="E143" s="1" t="n">
+        <v>3096245</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>96246</v>
+      </c>
+      <c r="B144" s="1" t="n">
+        <v>95012</v>
+      </c>
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D144" s="1" t="inlineStr">
+        <is>
+          <t>어이, 여기 공사 중이여!</t>
+        </is>
+      </c>
+      <c r="E144" s="1" t="n">
+        <v>3096246</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>96247</v>
+      </c>
+      <c r="B145" s="1" t="n">
+        <v>95012</v>
+      </c>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D145" s="1" t="inlineStr">
+        <is>
+          <t>어이쿠!</t>
+        </is>
+      </c>
+      <c r="E145" s="1" t="n">
+        <v>3096247</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>96248</v>
+      </c>
+      <c r="B146" s="1" t="n">
+        <v>95012</v>
+      </c>
+      <c r="C146" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D146" s="1" t="inlineStr">
+        <is>
+          <t>비켜, 비켜!</t>
+        </is>
+      </c>
+      <c r="E146" s="1" t="n">
+        <v>3096248</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>96249</v>
+      </c>
+      <c r="B147" s="1" t="n">
+        <v>95012</v>
+      </c>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D147" s="1" t="inlineStr">
+        <is>
+          <t>아이고 허리야!</t>
+        </is>
+      </c>
+      <c r="E147" s="1" t="n">
+        <v>3096249</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>96250</v>
+      </c>
+      <c r="B148" s="1" t="n">
+        <v>95012</v>
+      </c>
+      <c r="C148" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D148" s="1" t="inlineStr">
+        <is>
+          <t>일당 깎인다!</t>
+        </is>
+      </c>
+      <c r="E148" s="1" t="n">
+        <v>3096250</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>96251</v>
+      </c>
+      <c r="B149" s="1" t="n">
+        <v>95012</v>
+      </c>
+      <c r="C149" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D149" s="1" t="inlineStr">
+        <is>
+          <t>오늘 일당은 받아야 혀…</t>
+        </is>
+      </c>
+      <c r="E149" s="1" t="n">
+        <v>3096251</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>96252</v>
+      </c>
+      <c r="B150" s="1" t="n">
+        <v>95012</v>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D150" s="1" t="inlineStr">
+        <is>
+          <t>칼퇴다아~</t>
+        </is>
+      </c>
+      <c r="E150" s="1" t="n">
+        <v>3096252</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>96253</v>
+      </c>
+      <c r="B151" s="1" t="n">
+        <v>95012</v>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="inlineStr">
+        <is>
+          <t>조아쓰!! 가즈아!!</t>
+        </is>
+      </c>
+      <c r="E151" s="1" t="n">
+        <v>3096253</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>96254</v>
+      </c>
+      <c r="B152" s="1" t="n">
+        <v>95012</v>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="inlineStr">
+        <is>
+          <t>포크레인 출동!</t>
+        </is>
+      </c>
+      <c r="E152" s="1" t="n">
+        <v>3096254</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>96255</v>
+      </c>
+      <c r="B153" s="1" t="n">
+        <v>95013</v>
+      </c>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="inlineStr">
+        <is>
+          <t>츄르 인상 없인 일 안 한다냥!</t>
+        </is>
+      </c>
+      <c r="E153" s="1" t="n">
+        <v>3096255</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>96256</v>
+      </c>
+      <c r="B154" s="1" t="n">
+        <v>95013</v>
+      </c>
+      <c r="C154" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D154" s="1" t="inlineStr">
+        <is>
+          <t>투쟁!</t>
+        </is>
+      </c>
+      <c r="E154" s="1" t="n">
+        <v>3096256</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>96257</v>
+      </c>
+      <c r="B155" s="1" t="n">
+        <v>95013</v>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="inlineStr">
+        <is>
+          <t>냥!</t>
+        </is>
+      </c>
+      <c r="E155" s="1" t="n">
+        <v>3096202</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>96258</v>
+      </c>
+      <c r="B156" s="1" t="n">
+        <v>95013</v>
+      </c>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="inlineStr">
+        <is>
+          <t>노동 탄압이다!</t>
+        </is>
+      </c>
+      <c r="E156" s="1" t="n">
+        <v>3096258</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>96259</v>
+      </c>
+      <c r="B157" s="1" t="n">
+        <v>95013</v>
+      </c>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="inlineStr">
+        <is>
+          <t>캬악!</t>
+        </is>
+      </c>
+      <c r="E157" s="1" t="n">
+        <v>3096033</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>96260</v>
+      </c>
+      <c r="B158" s="1" t="n">
+        <v>95013</v>
+      </c>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="inlineStr">
+        <is>
+          <t>협상… 하자냥…</t>
+        </is>
+      </c>
+      <c r="E158" s="1" t="n">
+        <v>3096260</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>96261</v>
+      </c>
+      <c r="B159" s="1" t="n">
+        <v>95013</v>
+      </c>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="inlineStr">
+        <is>
+          <t>드르렁…</t>
+        </is>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>3096261</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>96262</v>
+      </c>
+      <c r="B160" s="1" t="n">
+        <v>95013</v>
+      </c>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D160" s="1" t="inlineStr">
+        <is>
+          <t>총파업이다냥!!</t>
+        </is>
+      </c>
+      <c r="E160" s="1" t="n">
+        <v>3096262</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>96263</v>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>95013</v>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="inlineStr">
+        <is>
+          <t>피켓 들어!</t>
+        </is>
+      </c>
+      <c r="E161" s="1" t="n">
+        <v>3096263</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>96264</v>
+      </c>
+      <c r="B162" s="1" t="n">
+        <v>95014</v>
+      </c>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="inlineStr">
+        <is>
+          <t>밥은 먹고 다니냐?</t>
+        </is>
+      </c>
+      <c r="E162" s="1" t="n">
+        <v>3096264</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>96265</v>
+      </c>
+      <c r="B163" s="1" t="n">
+        <v>95014</v>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="inlineStr">
+        <is>
+          <t>밥 먹어!</t>
+        </is>
+      </c>
+      <c r="E163" s="1" t="n">
+        <v>3096265</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>96266</v>
+      </c>
+      <c r="B164" s="1" t="n">
+        <v>95014</v>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D164" s="1" t="inlineStr">
+        <is>
+          <t>더 먹어!</t>
+        </is>
+      </c>
+      <c r="E164" s="1" t="n">
+        <v>3096266</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>96267</v>
+      </c>
+      <c r="B165" s="1" t="n">
+        <v>95014</v>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="inlineStr">
+        <is>
+          <t>아이고!</t>
+        </is>
+      </c>
+      <c r="E165" s="1" t="n">
+        <v>3096267</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>96268</v>
+      </c>
+      <c r="B166" s="1" t="n">
+        <v>95014</v>
+      </c>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t>밥이 식잖아!</t>
+        </is>
+      </c>
+      <c r="E166" s="1" t="n">
+        <v>3096268</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>96269</v>
+      </c>
+      <c r="B167" s="1" t="n">
+        <v>95014</v>
+      </c>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="inlineStr">
+        <is>
+          <t>국 식는다…</t>
+        </is>
+      </c>
+      <c r="E167" s="1" t="n">
+        <v>3096269</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>96270</v>
+      </c>
+      <c r="B168" s="1" t="n">
+        <v>95014</v>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="inlineStr">
+        <is>
+          <t>설거지는 너희가 해!</t>
+        </is>
+      </c>
+      <c r="E168" s="1" t="n">
+        <v>3096270</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>96271</v>
+      </c>
+      <c r="B169" s="1" t="n">
+        <v>95014</v>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="inlineStr">
+        <is>
+          <t>밥은… 먹고 다니냐?</t>
+        </is>
+      </c>
+      <c r="E169" s="1" t="n">
+        <v>3096271</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>96272</v>
+      </c>
+      <c r="B170" s="1" t="n">
+        <v>95014</v>
+      </c>
+      <c r="C170" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D170" s="1" t="inlineStr">
+        <is>
+          <t>고봉밥 나간다!</t>
+        </is>
+      </c>
+      <c r="E170" s="1" t="n">
+        <v>3096272</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>96273</v>
+      </c>
+      <c r="B171" s="1" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="inlineStr">
+        <is>
+          <t>바닷속이 더 좋다냥~</t>
+        </is>
+      </c>
+      <c r="E171" s="1" t="n">
+        <v>3096273</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>96274</v>
+      </c>
+      <c r="B172" s="1" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="inlineStr">
+        <is>
+          <t>찰싹!</t>
+        </is>
+      </c>
+      <c r="E172" s="1" t="n">
+        <v>3096274</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>96275</v>
+      </c>
+      <c r="B173" s="1" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="inlineStr">
+        <is>
+          <t>냥!</t>
+        </is>
+      </c>
+      <c r="E173" s="1" t="n">
+        <v>3096202</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>96276</v>
+      </c>
+      <c r="B174" s="1" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="inlineStr">
+        <is>
+          <t>비늘이!</t>
+        </is>
+      </c>
+      <c r="E174" s="1" t="n">
+        <v>3096276</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>96277</v>
+      </c>
+      <c r="B175" s="1" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="inlineStr">
+        <is>
+          <t>캬악!</t>
+        </is>
+      </c>
+      <c r="E175" s="1" t="n">
+        <v>3096033</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>96278</v>
+      </c>
+      <c r="B176" s="1" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="inlineStr">
+        <is>
+          <t>거품이 되어…</t>
+        </is>
+      </c>
+      <c r="E176" s="1" t="n">
+        <v>3096278</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>96279</v>
+      </c>
+      <c r="B177" s="1" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>냐아아~</t>
+        </is>
+      </c>
+      <c r="E177" s="1" t="n">
+        <v>3096207</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>96280</v>
+      </c>
+      <c r="B178" s="1" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C178" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D178" s="1" t="inlineStr">
+        <is>
+          <t>파도야 와라냥!</t>
+        </is>
+      </c>
+      <c r="E178" s="1" t="n">
+        <v>3096280</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>96281</v>
+      </c>
+      <c r="B179" s="1" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C179" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D179" s="1" t="inlineStr">
+        <is>
+          <t>언더 더 씨~</t>
+        </is>
+      </c>
+      <c r="E179" s="1" t="n">
+        <v>3096281</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>96282</v>
+      </c>
+      <c r="B180" s="1" t="n">
+        <v>95016</v>
+      </c>
+      <c r="C180" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="inlineStr">
+        <is>
+          <t>잠수 준비 완료냥.</t>
+        </is>
+      </c>
+      <c r="E180" s="1" t="n">
+        <v>3096282</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>96283</v>
+      </c>
+      <c r="B181" s="1" t="n">
+        <v>95016</v>
+      </c>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="inlineStr">
+        <is>
+          <t>보글!</t>
+        </is>
+      </c>
+      <c r="E181" s="1" t="n">
+        <v>3096283</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>96284</v>
+      </c>
+      <c r="B182" s="1" t="n">
+        <v>95016</v>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="inlineStr">
+        <is>
+          <t>냥!</t>
+        </is>
+      </c>
+      <c r="E182" s="1" t="n">
+        <v>3096202</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>96285</v>
+      </c>
+      <c r="B183" s="1" t="n">
+        <v>95016</v>
+      </c>
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="inlineStr">
+        <is>
+          <t>유리에 금이!</t>
+        </is>
+      </c>
+      <c r="E183" s="1" t="n">
+        <v>3096285</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>96286</v>
+      </c>
+      <c r="B184" s="1" t="n">
+        <v>95016</v>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="inlineStr">
+        <is>
+          <t>캬악!</t>
+        </is>
+      </c>
+      <c r="E184" s="1" t="n">
+        <v>3096033</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>96287</v>
+      </c>
+      <c r="B185" s="1" t="n">
+        <v>95016</v>
+      </c>
+      <c r="C185" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D185" s="1" t="inlineStr">
+        <is>
+          <t>부상한다냥…</t>
+        </is>
+      </c>
+      <c r="E185" s="1" t="n">
+        <v>3096287</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>96288</v>
+      </c>
+      <c r="B186" s="1" t="n">
+        <v>95016</v>
+      </c>
+      <c r="C186" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="inlineStr">
+        <is>
+          <t>보글보글…</t>
+        </is>
+      </c>
+      <c r="E186" s="1" t="n">
+        <v>3096288</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>96289</v>
+      </c>
+      <c r="B187" s="1" t="n">
+        <v>95016</v>
+      </c>
+      <c r="C187" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="inlineStr">
+        <is>
+          <t>핑―</t>
+        </is>
+      </c>
+      <c r="E187" s="1" t="n">
+        <v>3096289</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>96290</v>
+      </c>
+      <c r="B188" s="1" t="n">
+        <v>95016</v>
+      </c>
+      <c r="C188" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="inlineStr">
+        <is>
+          <t>닻 내려라냥!</t>
+        </is>
+      </c>
+      <c r="E188" s="1" t="n">
+        <v>3096290</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>96291</v>
+      </c>
+      <c r="B189" s="1" t="n">
+        <v>95017</v>
+      </c>
+      <c r="C189" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="inlineStr">
+        <is>
+          <t>빠밤… 빠밤…</t>
+        </is>
+      </c>
+      <c r="E189" s="1" t="n">
+        <v>3096291</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>96292</v>
+      </c>
+      <c r="B190" s="1" t="n">
+        <v>95017</v>
+      </c>
+      <c r="C190" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="inlineStr">
+        <is>
+          <t>와앙!</t>
+        </is>
+      </c>
+      <c r="E190" s="1" t="n">
+        <v>3096292</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>96293</v>
+      </c>
+      <c r="B191" s="1" t="n">
+        <v>95017</v>
+      </c>
+      <c r="C191" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="inlineStr">
+        <is>
+          <t>냥!</t>
+        </is>
+      </c>
+      <c r="E191" s="1" t="n">
+        <v>3096202</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>96294</v>
+      </c>
+      <c r="B192" s="1" t="n">
+        <v>95017</v>
+      </c>
+      <c r="C192" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="inlineStr">
+        <is>
+          <t>지느러미가!</t>
+        </is>
+      </c>
+      <c r="E192" s="1" t="n">
+        <v>3096294</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>96295</v>
+      </c>
+      <c r="B193" s="1" t="n">
+        <v>95017</v>
+      </c>
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D193" s="1" t="inlineStr">
+        <is>
+          <t>캬악!</t>
+        </is>
+      </c>
+      <c r="E193" s="1" t="n">
+        <v>3096033</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>96296</v>
+      </c>
+      <c r="B194" s="1" t="n">
+        <v>95017</v>
+      </c>
+      <c r="C194" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D194" s="1" t="inlineStr">
+        <is>
+          <t>뚜루루뚜루…</t>
+        </is>
+      </c>
+      <c r="E194" s="1" t="n">
+        <v>3096296</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>96297</v>
+      </c>
+      <c r="B195" s="1" t="n">
+        <v>95017</v>
+      </c>
+      <c r="C195" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="inlineStr">
+        <is>
+          <t>냐아아~</t>
+        </is>
+      </c>
+      <c r="E195" s="1" t="n">
+        <v>3096207</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>96298</v>
+      </c>
+      <c r="B196" s="1" t="n">
+        <v>95017</v>
+      </c>
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t>샤크네이도다냥!</t>
+        </is>
+      </c>
+      <c r="E196" s="1" t="n">
+        <v>3096298</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>96299</v>
+      </c>
+      <c r="B197" s="1" t="n">
+        <v>95017</v>
+      </c>
+      <c r="C197" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="inlineStr">
+        <is>
+          <t>아기상어 출동!</t>
+        </is>
+      </c>
+      <c r="E197" s="1" t="n">
+        <v>3096299</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>96300</v>
+      </c>
+      <c r="B198" s="1" t="n">
+        <v>95018</v>
+      </c>
+      <c r="C198" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D198" s="1" t="inlineStr">
+        <is>
+          <t>포탑… 이쪽이 앞인가냥?</t>
+        </is>
+      </c>
+      <c r="E198" s="1" t="n">
+        <v>3096300</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>96301</v>
+      </c>
+      <c r="B199" s="1" t="n">
+        <v>95018</v>
+      </c>
+      <c r="C199" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D199" s="1" t="inlineStr">
+        <is>
+          <t>발사!</t>
+        </is>
+      </c>
+      <c r="E199" s="1" t="n">
+        <v>3096301</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>96302</v>
+      </c>
+      <c r="B200" s="1" t="n">
+        <v>95018</v>
+      </c>
+      <c r="C200" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D200" s="1" t="inlineStr">
+        <is>
+          <t>냥!</t>
+        </is>
+      </c>
+      <c r="E200" s="1" t="n">
+        <v>3096202</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>96303</v>
+      </c>
+      <c r="B201" s="1" t="n">
+        <v>95018</v>
+      </c>
+      <c r="C201" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="inlineStr">
+        <is>
+          <t>조준이 안 돼!</t>
+        </is>
+      </c>
+      <c r="E201" s="1" t="n">
+        <v>3096303</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>96304</v>
+      </c>
+      <c r="B202" s="1" t="n">
+        <v>95018</v>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="inlineStr">
+        <is>
+          <t>캬악!</t>
+        </is>
+      </c>
+      <c r="E202" s="1" t="n">
+        <v>3096033</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>96305</v>
+      </c>
+      <c r="B203" s="1" t="n">
+        <v>95018</v>
+      </c>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D203" s="1" t="inlineStr">
+        <is>
+          <t>포탑이 돌아간다…</t>
+        </is>
+      </c>
+      <c r="E203" s="1" t="n">
+        <v>3096305</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>96306</v>
+      </c>
+      <c r="B204" s="1" t="n">
+        <v>95018</v>
+      </c>
+      <c r="C204" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D204" s="1" t="inlineStr">
+        <is>
+          <t>냐아아~</t>
+        </is>
+      </c>
+      <c r="E204" s="1" t="n">
+        <v>3096207</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>96307</v>
+      </c>
+      <c r="B205" s="1" t="n">
+        <v>95018</v>
+      </c>
+      <c r="C205" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="inlineStr">
+        <is>
+          <t>전 포문 발사!</t>
+        </is>
+      </c>
+      <c r="E205" s="1" t="n">
+        <v>3096307</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>96308</v>
+      </c>
+      <c r="B206" s="1" t="n">
+        <v>95018</v>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="inlineStr">
+        <is>
+          <t>어… 거기 아닌데?</t>
+        </is>
+      </c>
+      <c r="E206" s="1" t="n">
+        <v>3096308</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>96309</v>
+      </c>
+      <c r="B207" s="1" t="n">
+        <v>95019</v>
+      </c>
+      <c r="C207" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="inlineStr">
+        <is>
+          <t>라이언 이병, 임무 수행 중이다냥!</t>
+        </is>
+      </c>
+      <c r="E207" s="1" t="n">
+        <v>3096309</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>96310</v>
+      </c>
+      <c r="B208" s="1" t="n">
+        <v>95019</v>
+      </c>
+      <c r="C208" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D208" s="1" t="inlineStr">
+        <is>
+          <t>어흥!</t>
+        </is>
+      </c>
+      <c r="E208" s="1" t="n">
+        <v>3096310</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>96311</v>
+      </c>
+      <c r="B209" s="1" t="n">
+        <v>95019</v>
+      </c>
+      <c r="C209" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="inlineStr">
+        <is>
+          <t>돌격!</t>
+        </is>
+      </c>
+      <c r="E209" s="1" t="n">
+        <v>3096311</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>96312</v>
+      </c>
+      <c r="B210" s="1" t="n">
+        <v>95019</v>
+      </c>
+      <c r="C210" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D210" s="1" t="inlineStr">
+        <is>
+          <t>갈기가!</t>
+        </is>
+      </c>
+      <c r="E210" s="1" t="n">
+        <v>3096312</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>96313</v>
+      </c>
+      <c r="B211" s="1" t="n">
+        <v>95019</v>
+      </c>
+      <c r="C211" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D211" s="1" t="inlineStr">
+        <is>
+          <t>위생병!</t>
+        </is>
+      </c>
+      <c r="E211" s="1" t="n">
+        <v>3096313</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>96314</v>
+      </c>
+      <c r="B212" s="1" t="n">
+        <v>95019</v>
+      </c>
+      <c r="C212" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="inlineStr">
+        <is>
+          <t>이병… 구해 줘…</t>
+        </is>
+      </c>
+      <c r="E212" s="1" t="n">
+        <v>3096314</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>96315</v>
+      </c>
+      <c r="B213" s="1" t="n">
+        <v>95019</v>
+      </c>
+      <c r="C213" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D213" s="1" t="inlineStr">
+        <is>
+          <t>어흐응…</t>
+        </is>
+      </c>
+      <c r="E213" s="1" t="n">
+        <v>3096315</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>96316</v>
+      </c>
+      <c r="B214" s="1" t="n">
+        <v>95019</v>
+      </c>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D214" s="1" t="inlineStr">
+        <is>
+          <t>하쿠나 마타타!</t>
+        </is>
+      </c>
+      <c r="E214" s="1" t="n">
+        <v>3096316</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>96317</v>
+      </c>
+      <c r="B215" s="1" t="n">
+        <v>95019</v>
+      </c>
+      <c r="C215" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D215" s="1" t="inlineStr">
+        <is>
+          <t>사자후!!</t>
+        </is>
+      </c>
+      <c r="E215" s="1" t="n">
+        <v>3096317</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>96318</v>
+      </c>
+      <c r="B216" s="1" t="n">
+        <v>95020</v>
+      </c>
+      <c r="C216" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D216" s="1" t="inlineStr">
+        <is>
+          <t>츄르 담당만 남고 다 나가!!</t>
+        </is>
+      </c>
+      <c r="E216" s="1" t="n">
+        <v>3096318</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>96319</v>
+      </c>
+      <c r="B217" s="1" t="n">
+        <v>95020</v>
+      </c>
+      <c r="C217" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D217" s="1" t="inlineStr">
+        <is>
+          <t>냥!!</t>
+        </is>
+      </c>
+      <c r="E217" s="1" t="n">
+        <v>3096319</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>96320</v>
+      </c>
+      <c r="B218" s="1" t="n">
+        <v>95020</v>
+      </c>
+      <c r="C218" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D218" s="1" t="inlineStr">
+        <is>
+          <t>안 돼!!</t>
+        </is>
+      </c>
+      <c r="E218" s="1" t="n">
+        <v>3096320</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>96321</v>
+      </c>
+      <c r="B219" s="1" t="n">
+        <v>95020</v>
+      </c>
+      <c r="C219" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D219" s="1" t="inlineStr">
+        <is>
+          <t>작전이!</t>
+        </is>
+      </c>
+      <c r="E219" s="1" t="n">
+        <v>3096321</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>96322</v>
+      </c>
+      <c r="B220" s="1" t="n">
+        <v>95020</v>
+      </c>
+      <c r="C220" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D220" s="1" t="inlineStr">
+        <is>
+          <t>캬악!</t>
+        </is>
+      </c>
+      <c r="E220" s="1" t="n">
+        <v>3096033</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>96323</v>
+      </c>
+      <c r="B221" s="1" t="n">
+        <v>95020</v>
+      </c>
+      <c r="C221" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="inlineStr">
+        <is>
+          <t>이건… 반칙이다…</t>
+        </is>
+      </c>
+      <c r="E221" s="1" t="n">
+        <v>3096323</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>96324</v>
+      </c>
+      <c r="B222" s="1" t="n">
+        <v>95020</v>
+      </c>
+      <c r="C222" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="inlineStr">
+        <is>
+          <t>안경 어디 갔지…</t>
+        </is>
+      </c>
+      <c r="E222" s="1" t="n">
+        <v>3096324</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>96325</v>
+      </c>
+      <c r="B223" s="1" t="n">
+        <v>95020</v>
+      </c>
+      <c r="C223" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="inlineStr">
+        <is>
+          <t>누가 츄르를 먹었냥!!</t>
+        </is>
+      </c>
+      <c r="E223" s="1" t="n">
+        <v>3096325</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>96326</v>
+      </c>
+      <c r="B224" s="1" t="n">
+        <v>95020</v>
+      </c>
+      <c r="C224" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="inlineStr">
+        <is>
+          <t>연필 던진다!</t>
+        </is>
+      </c>
+      <c r="E224" s="1" t="n">
+        <v>3096326</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>96327</v>
+      </c>
+      <c r="B225" s="1" t="n">
+        <v>95021</v>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr">
+        <is>
+          <t>...수상한 쥐들이군.</t>
+        </is>
+      </c>
+      <c r="E225" s="1" t="n">
+        <v>3096327</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>96328</v>
+      </c>
+      <c r="B226" s="1" t="n">
+        <v>95021</v>
+      </c>
+      <c r="C226" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="inlineStr">
+        <is>
+          <t>삐빅!</t>
+        </is>
+      </c>
+      <c r="E226" s="1" t="n">
+        <v>3096328</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>96329</v>
+      </c>
+      <c r="B227" s="1" t="n">
+        <v>95021</v>
+      </c>
+      <c r="C227" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="inlineStr">
+        <is>
+          <t>조사한다!</t>
+        </is>
+      </c>
+      <c r="E227" s="1" t="n">
+        <v>3096329</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>96330</v>
+      </c>
+      <c r="B228" s="1" t="n">
+        <v>95021</v>
+      </c>
+      <c r="C228" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D228" s="1" t="inlineStr">
+        <is>
+          <t>나 크루원이야!</t>
+        </is>
+      </c>
+      <c r="E228" s="1" t="n">
+        <v>3096330</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>96331</v>
+      </c>
+      <c r="B229" s="1" t="n">
+        <v>95021</v>
+      </c>
+      <c r="C229" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="inlineStr">
+        <is>
+          <t>으악!</t>
+        </is>
+      </c>
+      <c r="E229" s="1" t="n">
+        <v>3096331</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>96332</v>
+      </c>
+      <c r="B230" s="1" t="n">
+        <v>95021</v>
+      </c>
+      <c r="C230" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="inlineStr">
+        <is>
+          <t>임포스터는… 쥐였어…</t>
+        </is>
+      </c>
+      <c r="E230" s="1" t="n">
+        <v>3096332</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>96333</v>
+      </c>
+      <c r="B231" s="1" t="n">
+        <v>95021</v>
+      </c>
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="inlineStr">
+        <is>
+          <t>투표 결과…</t>
+        </is>
+      </c>
+      <c r="E231" s="1" t="n">
+        <v>3096333</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>96334</v>
+      </c>
+      <c r="B232" s="1" t="n">
+        <v>95021</v>
+      </c>
+      <c r="C232" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D232" s="1" t="inlineStr">
+        <is>
+          <t>긴급 회의!!</t>
+        </is>
+      </c>
+      <c r="E232" s="1" t="n">
+        <v>3096334</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>96335</v>
+      </c>
+      <c r="B233" s="1" t="n">
+        <v>95021</v>
+      </c>
+      <c r="C233" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="inlineStr">
+        <is>
+          <t>환풍구로!</t>
+        </is>
+      </c>
+      <c r="E233" s="1" t="n">
+        <v>3096335</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>96336</v>
+      </c>
+      <c r="B234" s="1" t="n">
+        <v>95022</v>
+      </c>
+      <c r="C234" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="inlineStr">
+        <is>
+          <t>눈이 뜨거워지는군냥.</t>
+        </is>
+      </c>
+      <c r="E234" s="1" t="n">
+        <v>3096336</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>96337</v>
+      </c>
+      <c r="B235" s="1" t="n">
+        <v>95022</v>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="inlineStr">
+        <is>
+          <t>삐융!</t>
+        </is>
+      </c>
+      <c r="E235" s="1" t="n">
+        <v>3096337</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>96338</v>
+      </c>
+      <c r="B236" s="1" t="n">
+        <v>95022</v>
+      </c>
+      <c r="C236" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D236" s="1" t="inlineStr">
+        <is>
+          <t>냥!</t>
+        </is>
+      </c>
+      <c r="E236" s="1" t="n">
+        <v>3096202</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>96339</v>
+      </c>
+      <c r="B237" s="1" t="n">
+        <v>95022</v>
+      </c>
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D237" s="1" t="inlineStr">
+        <is>
+          <t>눈부셔!</t>
+        </is>
+      </c>
+      <c r="E237" s="1" t="n">
+        <v>3096339</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>96340</v>
+      </c>
+      <c r="B238" s="1" t="n">
+        <v>95022</v>
+      </c>
+      <c r="C238" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D238" s="1" t="inlineStr">
+        <is>
+          <t>캬악!</t>
+        </is>
+      </c>
+      <c r="E238" s="1" t="n">
+        <v>3096033</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>96341</v>
+      </c>
+      <c r="B239" s="1" t="n">
+        <v>95022</v>
+      </c>
+      <c r="C239" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D239" s="1" t="inlineStr">
+        <is>
+          <t>은하로 돌아간다냥…</t>
+        </is>
+      </c>
+      <c r="E239" s="1" t="n">
+        <v>3096341</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>96342</v>
+      </c>
+      <c r="B240" s="1" t="n">
+        <v>95022</v>
+      </c>
+      <c r="C240" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D240" s="1" t="inlineStr">
+        <is>
+          <t>우이아…</t>
+        </is>
+      </c>
+      <c r="E240" s="1" t="n">
+        <v>3096342</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>96343</v>
+      </c>
+      <c r="B241" s="1" t="n">
+        <v>95022</v>
+      </c>
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="inlineStr">
+        <is>
+          <t>우이아이아~</t>
+        </is>
+      </c>
+      <c r="E241" s="1" t="n">
+        <v>3096343</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>96344</v>
+      </c>
+      <c r="B242" s="1" t="n">
+        <v>95022</v>
+      </c>
+      <c r="C242" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D242" s="1" t="inlineStr">
+        <is>
+          <t>레이저 발사!</t>
+        </is>
+      </c>
+      <c r="E242" s="1" t="n">
+        <v>3096344</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>96345</v>
+      </c>
+      <c r="B243" s="1" t="n">
+        <v>95023</v>
+      </c>
+      <c r="C243" s="1" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="inlineStr">
+        <is>
+          <t>싫어.</t>
+        </is>
+      </c>
+      <c r="E243" s="1" t="n">
+        <v>3096345</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>96346</v>
+      </c>
+      <c r="B244" s="1" t="n">
+        <v>95023</v>
+      </c>
+      <c r="C244" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D244" s="1" t="inlineStr">
+        <is>
+          <t>싫어.</t>
+        </is>
+      </c>
+      <c r="E244" s="1" t="n">
+        <v>3096345</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>96347</v>
+      </c>
+      <c r="B245" s="1" t="n">
+        <v>95023</v>
+      </c>
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="inlineStr">
+        <is>
+          <t>귀찮아.</t>
+        </is>
+      </c>
+      <c r="E245" s="1" t="n">
+        <v>3096347</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>96348</v>
+      </c>
+      <c r="B246" s="1" t="n">
+        <v>95023</v>
+      </c>
+      <c r="C246" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D246" s="1" t="inlineStr">
+        <is>
+          <t>짜증 나.</t>
+        </is>
+      </c>
+      <c r="E246" s="1" t="n">
+        <v>3096348</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>96349</v>
+      </c>
+      <c r="B247" s="1" t="n">
+        <v>95023</v>
+      </c>
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="inlineStr">
+        <is>
+          <t>하.</t>
+        </is>
+      </c>
+      <c r="E247" s="1" t="n">
+        <v>3096349</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>96350</v>
+      </c>
+      <c r="B248" s="1" t="n">
+        <v>95023</v>
+      </c>
+      <c r="C248" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="inlineStr">
+        <is>
+          <t>재밌었던 적 한 번 있었지. 최악이었어.</t>
+        </is>
+      </c>
+      <c r="E248" s="1" t="n">
+        <v>3096350</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>96351</v>
+      </c>
+      <c r="B249" s="1" t="n">
+        <v>95023</v>
+      </c>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="inlineStr">
+        <is>
+          <t>…싫어.</t>
+        </is>
+      </c>
+      <c r="E249" s="1" t="n">
+        <v>3096351</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>96352</v>
+      </c>
+      <c r="B250" s="1" t="n">
+        <v>95023</v>
+      </c>
+      <c r="C250" s="1" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="inlineStr">
+        <is>
+          <t>전부 싫어.</t>
+        </is>
+      </c>
+      <c r="E250" s="1" t="n">
+        <v>3096352</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>96353</v>
+      </c>
+      <c r="B251" s="1" t="n">
+        <v>95023</v>
+      </c>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="inlineStr">
+        <is>
+          <t>싫다고.</t>
+        </is>
+      </c>
+      <c r="E251" s="1" t="n">
+        <v>3096353</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3488,7 +8299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:S87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3500,6 +8311,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3558,6 +8370,46 @@
           <t>전용 대사 키</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>밈 패턴 (Boss.Meme.cs)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>그림 (BossMeme)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>그림 크기</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>색</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>팝업 글</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>팝업 글 키</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>패턴 값 1</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>패턴 값 2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -3615,6 +8467,46 @@
           <t>line_sk</t>
         </is>
       </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>popup</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>popup_sk</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -3670,6 +8562,46 @@
       <c r="K3" s="1" t="inlineStr">
         <is>
           <t>int</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
         </is>
       </c>
     </row>
@@ -4803,6 +9735,3732 @@
       </c>
       <c r="K33" s="1" t="n">
         <v>3200004</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Chipi_Chapa</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 치피치피 차파차파 (2024 춤추는 고양이 밈): 박자마다 좌우로 흔들며 둘레 충격파</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>치피치피 차파차파</t>
+        </is>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>3100030</v>
+      </c>
+      <c r="J34" s="1" t="n"/>
+      <c r="K34" s="1" t="n"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>bm_note</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>#f2a7c3</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>치피치피 차파차파!</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>4200001</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Happy_Rain</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 해피 고양이 (2023): 작은 해피 고양이 8마리가 떨어져 통통 뛰어다님</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>해피 고양이 대량 강하</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>3100031</v>
+      </c>
+      <c r="J35" s="1" t="n"/>
+      <c r="K35" s="1" t="n"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>bm_happy_mini</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>90</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>#f3efe6</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>해피해피~</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>4200002</v>
+      </c>
+      <c r="R35" t="n">
+        <v>4</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Huh_Cat</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 허? 고양이 (2023 Huh cat): 크게 "허?" → 주변 쥐가 놀라 날아감</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>허? 고양이</t>
+        </is>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>3100032</v>
+      </c>
+      <c r="J36" s="1" t="n"/>
+      <c r="K36" s="1" t="n"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Shout</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>#e8c07a</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>허?</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>4200003</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Pop_Pop</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 팝캣 (2020): 입을 뻥뻥 → 소리 고리를 쥐에게 날림</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>팝팝팝</t>
+        </is>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>3100033</v>
+      </c>
+      <c r="J37" s="1" t="n"/>
+      <c r="K37" s="1" t="n"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Throw</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>bm_pop_wave</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>90</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>#9fc6e8</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>팝!</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>4200004</v>
+      </c>
+      <c r="R37" t="n">
+        <v>30</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Pop_Clicker</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>[필살] popcat.click 클릭 대회 (2020): 거대 마우스 커서가 쥐 무리를 연타</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>팝캣 클릭 대회</t>
+        </is>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>3100034</v>
+      </c>
+      <c r="J38" s="1" t="n"/>
+      <c r="K38" s="1" t="n"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>bm_cursor</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>110</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>#f0a65a</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>클릭!</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>4200005</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Vibing_Cat</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 고개 까딱 고양이 (2020 Vibing Cat): 화면 안 쥐가 전부 같이 까딱거리며 멈춤</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>고개 까딱 고양이</t>
+        </is>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>3100035</v>
+      </c>
+      <c r="J39" s="1" t="n"/>
+      <c r="K39" s="1" t="n"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>bm_shades</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>110</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>#9fd3a8</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>까딱 까딱~</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>4200006</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Rock_Throw</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>[두 번째 공격] 돌멩이 3개</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>돌멩이 투척</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>3100036</v>
+      </c>
+      <c r="J40" s="1" t="n"/>
+      <c r="K40" s="1" t="n"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Throw</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>bm_rock</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>70</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>#9a8a7a</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>쿵!</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>4200007</v>
+      </c>
+      <c r="R40" t="n">
+        <v>20</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Fire_Discovery</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 자기 횃불에 놀란 원시인: 제자리에 불바다 장판</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G41" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>불의 발견</t>
+        </is>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>3100037</v>
+      </c>
+      <c r="J41" s="1" t="n"/>
+      <c r="K41" s="1" t="n"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>@grill</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>#f0a05a</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>앗 뜨거!!</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>4200008</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Return_To_Monke</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>[필살] Return to Monke (2020): 원숭이 4마리 소환 → 쥐에게 달려가 펑</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" s="1" t="inlineStr">
+        <is>
+          <t>원숭이로 돌아가자</t>
+        </is>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>3100038</v>
+      </c>
+      <c r="J42" s="1" t="n"/>
+      <c r="K42" s="1" t="n"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>bm_monke</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>90</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>#a07850</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>우가우가!</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>4200009</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Extinction</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 공룡 멸종 운석: 아주 큰 운석 하나</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>공룡 멸종 운석</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>3100039</v>
+      </c>
+      <c r="J43" s="1" t="n"/>
+      <c r="K43" s="1" t="n"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>bm_meteor</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>380</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>#e8743a</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>멸종이다!!</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>4200010</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Hold_Up</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 쥬라기 월드 손 내밀기 장면 (2015): 손을 내밀어 주변 쥐를 멈춤</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>340</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
+        <is>
+          <t>랩터 진정시키기</t>
+        </is>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>3100040</v>
+      </c>
+      <c r="J44" s="1" t="n"/>
+      <c r="K44" s="1" t="n"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Shout</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>bm_stop</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>90</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>#6f8a5a</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>워워… 진정해.</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>4200011</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Clever_Girl</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 쥬라기 공원 "Clever girl" (1993): 수풀에서 랩터 3마리</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" s="1" t="inlineStr">
+        <is>
+          <t>영리한 녀석</t>
+        </is>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>3100041</v>
+      </c>
+      <c r="J45" s="1" t="n"/>
+      <c r="K45" s="1" t="n"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>bm_raptor</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>110</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>#7a9a4a</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>영리한 녀석…</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>4200012</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Tranq_Dart</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 마취총 8발</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>마취총 연사</t>
+        </is>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>3100042</v>
+      </c>
+      <c r="J46" s="1" t="n"/>
+      <c r="K46" s="1" t="n"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Throw</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>bm_dart</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>60</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>#d0503a</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>푹!</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>4200013</v>
+      </c>
+      <c r="R46" t="n">
+        <v>10</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Trex_Dance</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 공룡 풍선옷 춤 영상: 빙글빙글 흐느적 춤추며 다가옴</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
+          <t>공룡탈 댄스</t>
+        </is>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>3100043</v>
+      </c>
+      <c r="J47" s="1" t="n"/>
+      <c r="K47" s="1" t="n"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Spin</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>#7cb86a</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>둠칫둠칫!</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>4200014</v>
+      </c>
+      <c r="R47" t="n">
+        <v>220</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Tiny_Arms</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 티렉스 짧은 팔 밈: 팔이 안 닿아 분해서 3번 쿵쿵 점프</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>짧은 팔의 분노</t>
+        </is>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>3100044</v>
+      </c>
+      <c r="J48" s="1" t="n"/>
+      <c r="K48" s="1" t="n"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>#5a9a4a</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>팔이… 안 닿아…!</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>4200015</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Deflate</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 공룡탈 바람 빠짐: 풍선처럼 이리저리 쌩쌩</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>바람 빠진 공룡</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>3100045</v>
+      </c>
+      <c r="J49" s="1" t="n"/>
+      <c r="K49" s="1" t="n"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>#9ad08a</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>푸쉬이이~</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>4200016</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1100</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Excavator</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 굴착기 버킷이 쥐 무리를 퍼 올림</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="1" t="inlineStr">
+        <is>
+          <t>포크레인 퍼 올리기</t>
+        </is>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>3100046</v>
+      </c>
+      <c r="J50" s="1" t="n"/>
+      <c r="K50" s="1" t="n"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>bm_bucket</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>200</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>#e0b23a</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>퍼 올려!</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>4200017</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Concrete</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 시멘트 장판 3곳 (오래 서 있으면 굳어 기절)</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" s="1" t="inlineStr">
+        <is>
+          <t>레미콘 타설</t>
+        </is>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>3100047</v>
+      </c>
+      <c r="J51" s="1" t="n"/>
+      <c r="K51" s="1" t="n"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>bm_concrete</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>#9a9a9a</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>굳는다!</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>4200018</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>Joa_Ssu</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>[필살] "조아쓰" 기합 밈 (2020): 기합 → 6초 동안 받는 피해 ×0.4</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t>조아쓰!!</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>3100048</v>
+      </c>
+      <c r="J52" s="1" t="n"/>
+      <c r="K52" s="1" t="n"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>bm_joassu</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>90</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>#f2c84a</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>조아쓰!!</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>4200019</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Picket</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 피켓 4개가 떨어져 3초 꽂혀 있음</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>피켓 시위</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>3100049</v>
+      </c>
+      <c r="J53" s="1" t="n"/>
+      <c r="K53" s="1" t="n"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>bm_picket</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>120</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>#c9564a</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>투쟁!</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>4200020</v>
+      </c>
+      <c r="R53" t="n">
+        <v>5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>Churu_Raise</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 확성기 외침</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H54" s="1" t="inlineStr">
+        <is>
+          <t>츄르 인상 요구</t>
+        </is>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>3100050</v>
+      </c>
+      <c r="J54" s="1" t="n"/>
+      <c r="K54" s="1" t="n"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Shout</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>bm_megaphone</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>90</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>#e86a5a</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>츄르 인상하라!!</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>4200021</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>Lie_Down</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 낮잠 구름 장판 3곳 (안에 있으면 같이 잠듦)</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H55" s="1" t="inlineStr">
+        <is>
+          <t>드러눕기 투쟁</t>
+        </is>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>3100051</v>
+      </c>
+      <c r="J55" s="1" t="n"/>
+      <c r="K55" s="1" t="n"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>bm_zzz</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>#a6b4d8</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>드르렁…</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>4200022</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Rice_Bowl</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>[두 번째 공격] 공깃밥 3개</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>공깃밥 투척</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>3100052</v>
+      </c>
+      <c r="J56" s="1" t="n"/>
+      <c r="K56" s="1" t="n"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Throw</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>bm_rice_bowl</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>70</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>#e8e0d0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>밥 먹어!</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>4200023</v>
+      </c>
+      <c r="R56" t="n">
+        <v>20</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>Gobong</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 고봉밥 4그릇</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G57" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>고봉밥 투하</t>
+        </is>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>3100053</v>
+      </c>
+      <c r="J57" s="1" t="n"/>
+      <c r="K57" s="1" t="n"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>bm_rice_mountain</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>160</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>#f4efe2</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>고봉밥!</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>4200024</v>
+      </c>
+      <c r="R57" t="n">
+        <v>5</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>Did_You_Eat</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 살인의 추억 "밥은 먹고 다니냐?" (2003): 화면 안 쥐 전부 숙연해짐</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
+        <is>
+          <t>밥은 먹고 다니냐?</t>
+        </is>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>3100054</v>
+      </c>
+      <c r="J58" s="1" t="n"/>
+      <c r="K58" s="1" t="n"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>#f6d58a</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>밥은 먹고 다니냐?</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>4200025</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>Ladle_Spin</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 국자를 들고 빙글빙글</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" s="1" t="inlineStr">
+        <is>
+          <t>국자 회오리</t>
+        </is>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>3100055</v>
+      </c>
+      <c r="J59" s="1" t="n"/>
+      <c r="K59" s="1" t="n"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Spin</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>bm_ladle</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>110</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>#e57b7b</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>국자 회오리!</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>4200026</v>
+      </c>
+      <c r="R59" t="n">
+        <v>260</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>Bubble_Shot</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>[두 번째 공격] 물방울 4개</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="1" t="inlineStr">
+        <is>
+          <t>물방울 발사</t>
+        </is>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>3100056</v>
+      </c>
+      <c r="J60" s="1" t="n"/>
+      <c r="K60" s="1" t="n"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Throw</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>bm_bubble</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>70</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>#9ad8e8</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>뽀글!</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>4200027</v>
+      </c>
+      <c r="R60" t="n">
+        <v>20</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>Under_The_Sea</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 인어공주 "Under the Sea": 물방울 5개가 쥐에게 둥실둥실 다가가 펑</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H61" s="1" t="inlineStr">
+        <is>
+          <t>언더 더 씨</t>
+        </is>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>3100057</v>
+      </c>
+      <c r="J61" s="1" t="n"/>
+      <c r="K61" s="1" t="n"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>bm_bubble</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>90</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>#6cc4c0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>언더 더 씨~♪</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>4200028</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>Tidal_Wave</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 가로로 쓸고 가는 해일</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H62" s="1" t="inlineStr">
+        <is>
+          <t>해일</t>
+        </is>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>3100058</v>
+      </c>
+      <c r="J62" s="1" t="n"/>
+      <c r="K62" s="1" t="n"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Sweep</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>bm_wave</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>150</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>#4a9ad0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>촤아악!</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>4200029</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>Fish_Slap</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 몬티 파이튼 생선 따귀 춤 (1972): 커다란 고등어 4마리가 날아다님</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" s="1" t="inlineStr">
+        <is>
+          <t>생선 따귀</t>
+        </is>
+      </c>
+      <c r="I63" s="1" t="n">
+        <v>3100059</v>
+      </c>
+      <c r="J63" s="1" t="n"/>
+      <c r="K63" s="1" t="n"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>bm_fish</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>130</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>#a8b8c8</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>생선 따귀!</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>4200030</v>
+      </c>
+      <c r="R63" t="n">
+        <v>520</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>Anchor_Drop</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 닻 3개</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H64" s="1" t="inlineStr">
+        <is>
+          <t>닻 내려!</t>
+        </is>
+      </c>
+      <c r="I64" s="1" t="n">
+        <v>3100060</v>
+      </c>
+      <c r="J64" s="1" t="n"/>
+      <c r="K64" s="1" t="n"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>bm_anchor</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>150</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>#7a8a9a</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>닻 내려!</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>4200031</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>Sonar_Ping</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 잠수함 소나: 큰 충격파 4번</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>440</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" s="1" t="inlineStr">
+        <is>
+          <t>소나 핑</t>
+        </is>
+      </c>
+      <c r="I65" s="1" t="n">
+        <v>3100061</v>
+      </c>
+      <c r="J65" s="1" t="n"/>
+      <c r="K65" s="1" t="n"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>#6ad0c8</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>핑―</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>4200032</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>Octo_Ink</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 먹물 장판 3곳</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G66" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H66" s="1" t="inlineStr">
+        <is>
+          <t>문어 먹물</t>
+        </is>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>3100062</v>
+      </c>
+      <c r="J66" s="1" t="n"/>
+      <c r="K66" s="1" t="n"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>bm_ink</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>#3a3a4a</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>먹물!</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>4200033</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>Baby_Shark</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 아기상어 (2016): 아기상어 4마리</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H67" s="1" t="inlineStr">
+        <is>
+          <t>아기상어</t>
+        </is>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>3100063</v>
+      </c>
+      <c r="J67" s="1" t="n"/>
+      <c r="K67" s="1" t="n"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>bm_baby_shark</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>90</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>#f2d34a</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>아기상어 뚜루루뚜루~</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>4200034</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>Jaws_Dash</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 죠스 테마 (1975): 등지느러미를 세우고 4번 돌진</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G68" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H68" s="1" t="inlineStr">
+        <is>
+          <t>죠스 돌진</t>
+        </is>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>3100064</v>
+      </c>
+      <c r="J68" s="1" t="n"/>
+      <c r="K68" s="1" t="n"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>bm_fin</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>90</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>#5a7a9a</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>빠밤… 빠밤…</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>4200035</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>Sharknado</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 샤크네이도 (2013): 상어 회오리가 쥐를 빨아들였다가 펑</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1" t="inlineStr">
+        <is>
+          <t>샤크네이도</t>
+        </is>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>3100065</v>
+      </c>
+      <c r="J69" s="1" t="n"/>
+      <c r="K69" s="1" t="n"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>bm_sharknado</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>260</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>#8a9aaa</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>샤크네이도!!</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>4200036</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>Wrong_Way</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 포탑이 엉뚱한 방향: 포탄 5발이 이상한 데 떨어짐</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G70" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H70" s="1" t="inlineStr">
+        <is>
+          <t>엉뚱한 포격</t>
+        </is>
+      </c>
+      <c r="I70" s="1" t="n">
+        <v>3100066</v>
+      </c>
+      <c r="J70" s="1" t="n"/>
+      <c r="K70" s="1" t="n"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Throw</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>bm_shell</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>60</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>#c8a04a</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>어… 거기 아닌데?</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>4200037</v>
+      </c>
+      <c r="R70" t="n">
+        <v>380</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Barrage</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 가로줄 포격 8발</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F71" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G71" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H71" s="1" t="inlineStr">
+        <is>
+          <t>일제 포격</t>
+        </is>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>3100067</v>
+      </c>
+      <c r="J71" s="1" t="n"/>
+      <c r="K71" s="1" t="n"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Sweep</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>bm_shell</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>90</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>#e88a3a</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>쾅!</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>4200038</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>No_Scope</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 360 노스코프 (게임 밈): 빙글 돌며 사방으로 8발</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G72" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H72" s="1" t="inlineStr">
+        <is>
+          <t>360 노스코프</t>
+        </is>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>3100068</v>
+      </c>
+      <c r="J72" s="1" t="n"/>
+      <c r="K72" s="1" t="n"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>#ffd25a</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>360 노스코프!!</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>4200039</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>Lion_Roar</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 사자후</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G73" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H73" s="1" t="inlineStr">
+        <is>
+          <t>사자후</t>
+        </is>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>3100069</v>
+      </c>
+      <c r="J73" s="1" t="n"/>
+      <c r="K73" s="1" t="n"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Shout</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>#d9a441</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>어흥!!</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>4200040</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>Circle_Of_Life</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 라이온 킹 "Circle of Life" (1994): 화면 안 쥐 전부 감동해서 멈춤</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="1" t="inlineStr">
+        <is>
+          <t>생명의 순환</t>
+        </is>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>3100070</v>
+      </c>
+      <c r="J74" s="1" t="n"/>
+      <c r="K74" s="1" t="n"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>#ffcf6b</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>나~ 쥐 고냐~!!</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>4200041</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>Supply_Drop</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 라이언 일병 구하기 (1998): 낙하산 보급 상자 5개</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" s="1" t="inlineStr">
+        <is>
+          <t>이병 구하기 보급</t>
+        </is>
+      </c>
+      <c r="I75" s="1" t="n">
+        <v>3100071</v>
+      </c>
+      <c r="J75" s="1" t="n"/>
+      <c r="K75" s="1" t="n"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>bm_airdrop</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>140</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>#c8b88a</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>보급 왔다!</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>4200042</v>
+      </c>
+      <c r="R75" t="n">
+        <v>5</v>
+      </c>
+      <c r="S75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>Pencil_Throw</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 몰락 벙커 장면 (2004) 연필 던지기</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G76" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H76" s="1" t="inlineStr">
+        <is>
+          <t>연필 던지기</t>
+        </is>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>3100072</v>
+      </c>
+      <c r="J76" s="1" t="n"/>
+      <c r="K76" s="1" t="n"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Throw</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>bm_pencil</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>80</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>#e8c84a</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>연필 던짐!</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>4200043</v>
+      </c>
+      <c r="R76" t="n">
+        <v>40</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Bunker_Rant</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 몰락 벙커 분노 장면: 화면 안 쥐 전부 얼어붙음</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="1" t="inlineStr">
+        <is>
+          <t>벙커 분노</t>
+        </is>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>3100073</v>
+      </c>
+      <c r="J77" s="1" t="n"/>
+      <c r="K77" s="1" t="n"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>#c84a3a</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>다 나가!! 츄르 담당만 남아!!</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>4200044</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>Map_Slam</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 작전 지도 테이블 내리치기 3번</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1" t="inlineStr">
+        <is>
+          <t>작전 지도 쾅!</t>
+        </is>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>3100074</v>
+      </c>
+      <c r="J78" s="1" t="n"/>
+      <c r="K78" s="1" t="n"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Hop</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>#8a7a6a</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>쾅!! 작전 실패다!!</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>4200045</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>Vent</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 어몽어스 (2018) 환풍구: 사라졌다가 쥐 무리 한가운데로</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G79" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" s="1" t="inlineStr">
+        <is>
+          <t>환풍구 이동</t>
+        </is>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>3100075</v>
+      </c>
+      <c r="J79" s="1" t="n"/>
+      <c r="K79" s="1" t="n"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Teleport</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>bm_vent</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>120</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>#d43b3b</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>환풍구!</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>4200046</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>Sus</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>[필살] "Sus" 투표: 쥐 6마리를 지목했다가 우주로 날려 버림</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1" t="inlineStr">
+        <is>
+          <t>수상해</t>
+        </is>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>3100076</v>
+      </c>
+      <c r="J80" s="1" t="n"/>
+      <c r="K80" s="1" t="n"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>bm_sus</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>#ff4a4a</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>수상해…</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>4200047</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>Lights_Out</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 어몽어스 전등 사보타주: 화면이 깜깜 → 쥐 전부 멈춤</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="1" t="inlineStr">
+        <is>
+          <t>전등 사보타주</t>
+        </is>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>3100077</v>
+      </c>
+      <c r="J81" s="1" t="n"/>
+      <c r="K81" s="1" t="n"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>bm_wrench</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>110</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>#20202a</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>전등 사보타주!</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>4200048</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>Laser_Eyes</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 레이저 눈 밈: 눈에서 빔 4발</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="1" t="inlineStr">
+        <is>
+          <t>레이저 눈</t>
+        </is>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>3100078</v>
+      </c>
+      <c r="J82" s="1" t="n"/>
+      <c r="K82" s="1" t="n"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>#ff3a3a</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>삐융!</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>4200049</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>OIIA</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>[필살] OIIA 빙글빙글 고양이 (2024)</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G83" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>우이아 고양이</t>
+        </is>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>3100079</v>
+      </c>
+      <c r="J83" s="1" t="n"/>
+      <c r="K83" s="1" t="n"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Spin</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>#b08aff</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>우이아이아~</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>4200050</v>
+      </c>
+      <c r="R83" t="n">
+        <v>330</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>Galaxy_Bang</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 은하 소용돌이가 쥐를 빨아들였다가 대폭발</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>340</v>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1" t="inlineStr">
+        <is>
+          <t>빅뱅</t>
+        </is>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>3100080</v>
+      </c>
+      <c r="J84" s="1" t="n"/>
+      <c r="K84" s="1" t="n"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Pull</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>260</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>#6b4ac8</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>빅뱅!!</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>4200051</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>No_Cat</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 그럼피 캣 "NO." (2012)</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>440</v>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G85" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H85" s="1" t="inlineStr">
+        <is>
+          <t>싫어.</t>
+        </is>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>3100081</v>
+      </c>
+      <c r="J85" s="1" t="n"/>
+      <c r="K85" s="1" t="n"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Shout</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>#5a6fa8</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>싫어.</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>4200052</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>Had_Fun_Once</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 그럼피 캣 "I had fun once. It was awful."</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="1" t="inlineStr">
+        <is>
+          <t>재미없어</t>
+        </is>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>3100082</v>
+      </c>
+      <c r="J86" s="1" t="n"/>
+      <c r="K86" s="1" t="n"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>#6a7fb8</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>재밌었던 적 한 번 있었지. 최악이었어.</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>4200053</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>Moon_Drop</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>[필살] 거대한 달 하나</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>480</v>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G87" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H87" s="1" t="inlineStr">
+        <is>
+          <t>달 떨어뜨리기</t>
+        </is>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>3100083</v>
+      </c>
+      <c r="J87" s="1" t="n"/>
+      <c r="K87" s="1" t="n"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>bm_moon</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>420</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>#c8c8d0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>달이다!!</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>4200054</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Boss" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Boss_Line" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Atk_Type" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Situation_Type" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss_Line" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atk_Type" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Situation_Type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -866,7 +866,7 @@
         <v>2.8</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>30.1</v>
+        <v>20.1</v>
       </c>
       <c r="N4" s="1" t="n">
         <v>300</v>
@@ -960,7 +960,7 @@
         <v>2.8</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>33.6</v>
+        <v>22.4</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>300</v>
@@ -1054,7 +1054,7 @@
         <v>2.8</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>42.4</v>
+        <v>28.3</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>300</v>
@@ -1148,7 +1148,7 @@
         <v>3.4</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>50.5</v>
+        <v>28.1</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>300</v>
@@ -1430,7 +1430,7 @@
         <v>3.4</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N10" s="1" t="n">
         <v>300</v>
@@ -1524,7 +1524,7 @@
         <v>3.4</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>45</v>
+        <v>40.8</v>
       </c>
       <c r="N11" s="1" t="n">
         <v>300</v>
@@ -1618,7 +1618,7 @@
         <v>2.8</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N12" s="1" t="n">
         <v>300</v>
@@ -1712,7 +1712,7 @@
         <v>2.8</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>45</v>
+        <v>41.4</v>
       </c>
       <c r="N13" s="1" t="n">
         <v>300</v>
@@ -1806,7 +1806,7 @@
         <v>2.9</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>48</v>
+        <v>26.7</v>
       </c>
       <c r="N14" s="1" t="n">
         <v>300</v>
@@ -1900,7 +1900,7 @@
         <v>2.9</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>300</v>
@@ -1994,7 +1994,7 @@
         <v>3.4</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>48</v>
+        <v>26.7</v>
       </c>
       <c r="N16" s="1" t="n">
         <v>300</v>
@@ -2088,7 +2088,7 @@
         <v>2.9</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>52</v>
+        <v>49.2</v>
       </c>
       <c r="N17" s="1" t="n">
         <v>300</v>
@@ -2182,7 +2182,7 @@
         <v>3.4</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>48</v>
+        <v>26.7</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>300</v>
@@ -2276,7 +2276,7 @@
         <v>3.5</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>300</v>
@@ -2370,7 +2370,7 @@
         <v>3.5</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>52</v>
+        <v>28.9</v>
       </c>
       <c r="N20" s="1" t="n">
         <v>300</v>
@@ -2464,7 +2464,7 @@
         <v>3.5</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>50</v>
+        <v>48.6</v>
       </c>
       <c r="N21" s="1" t="n">
         <v>300</v>
@@ -2558,7 +2558,7 @@
         <v>3.5</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>52</v>
+        <v>28.9</v>
       </c>
       <c r="N22" s="1" t="n">
         <v>300</v>
@@ -2652,7 +2652,7 @@
         <v>3.5</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>55</v>
+        <v>54.2</v>
       </c>
       <c r="N23" s="1" t="n">
         <v>300</v>
@@ -2746,7 +2746,7 @@
         <v>2.9</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="N24" s="1" t="n">
         <v>300</v>
@@ -2840,7 +2840,7 @@
         <v>3.5</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>52</v>
+        <v>34.7</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>300</v>
@@ -2934,7 +2934,7 @@
         <v>3.8</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="N26" s="1" t="n">
         <v>300</v>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -960,7 +960,7 @@
         <v>2.8</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>22.4</v>
+        <v>33.6</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>300</v>
@@ -1054,7 +1054,7 @@
         <v>2.8</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>28.3</v>
+        <v>42.4</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>300</v>
@@ -1148,7 +1148,7 @@
         <v>3.4</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>28.1</v>
+        <v>22.4</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>300</v>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -1148,7 +1148,7 @@
         <v>3.4</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>22.4</v>
+        <v>33.7</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>300</v>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -866,7 +866,7 @@
         <v>2.8</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>20.1</v>
+        <v>16.6</v>
       </c>
       <c r="N4" s="1" t="n">
         <v>300</v>
@@ -960,7 +960,7 @@
         <v>2.8</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>33.6</v>
+        <v>28</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>300</v>
@@ -1054,7 +1054,7 @@
         <v>2.8</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>42.4</v>
+        <v>35.3</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>300</v>
@@ -1148,7 +1148,7 @@
         <v>3.4</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>33.7</v>
+        <v>28.1</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>300</v>
@@ -1524,7 +1524,7 @@
         <v>3.4</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>40.8</v>
+        <v>25</v>
       </c>
       <c r="N11" s="1" t="n">
         <v>300</v>
@@ -1712,7 +1712,7 @@
         <v>2.8</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>41.4</v>
+        <v>40.8</v>
       </c>
       <c r="N13" s="1" t="n">
         <v>300</v>
@@ -1900,7 +1900,7 @@
         <v>2.9</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>46.7</v>
+        <v>27.8</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>300</v>
@@ -2088,7 +2088,7 @@
         <v>2.9</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>49.2</v>
+        <v>28.9</v>
       </c>
       <c r="N17" s="1" t="n">
         <v>300</v>
@@ -2276,7 +2276,7 @@
         <v>3.5</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>300</v>
@@ -2464,7 +2464,7 @@
         <v>3.5</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>48.6</v>
+        <v>27.8</v>
       </c>
       <c r="N21" s="1" t="n">
         <v>300</v>
@@ -2652,7 +2652,7 @@
         <v>3.5</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>54.2</v>
+        <v>30.6</v>
       </c>
       <c r="N23" s="1" t="n">
         <v>300</v>
@@ -2934,7 +2934,7 @@
         <v>3.8</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>64.90000000000001</v>
+        <v>36.1</v>
       </c>
       <c r="N26" s="1" t="n">
         <v>300</v>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss_Line" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atk_Type" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Situation_Type" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Boss" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Boss_Line" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Atk_Type" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Situation_Type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>32.4</v>
+        <v>36.1</v>
       </c>
       <c r="N9" s="1" t="n">
         <v>300</v>
@@ -1365,18 +1365,18 @@
       </c>
       <c r="U9" s="1" t="inlineStr">
         <is>
-          <t>Maxwell_Drop</t>
+          <t>Buttered_Cat</t>
         </is>
       </c>
       <c r="V9" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X9" s="1" t="inlineStr">
         <is>
-          <t>(미사용 2026-10-19: 16~30층 고양이 연구소로 교체, 테스트 패널로만) 30층 보스. 무중력 파동 (주변 쥐가 떠올랐다 떨어지며 기절) · 덮치기. 30층 뒤로는 5층 보스부터 다시 반복</t>
+          <t>100층 보스 (보스 개편 2026-10-22): 예전 우주 고양이 사령관, 맥스웰 드롭 → 버터 고양이(잼 식빵 고양이 회전)</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="X10" s="1" t="inlineStr">
         <is>
-          <t>25층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Chipi_Chapa · Happy_Rain · Huh_Cat</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 25층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Chipi_Chapa · Happy_Rain · Huh_Cat</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="X11" s="1" t="inlineStr">
         <is>
-          <t>30층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Pop_Pop · Pop_Clicker · Vibing_Cat</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 30층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Pop_Pop · Pop_Clicker · Vibing_Cat</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="X12" s="1" t="inlineStr">
         <is>
-          <t>35층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Fire_Discovery · Return_To_Monke · Extinction</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 35층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Fire_Discovery · Return_To_Monke · Extinction</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="X13" s="1" t="inlineStr">
         <is>
-          <t>40층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Hold_Up · Clever_Girl · Tranq_Dart</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 40층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Hold_Up · Clever_Girl · Tranq_Dart</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="X14" s="1" t="inlineStr">
         <is>
-          <t>45층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Trex_Dance · Tiny_Arms · Deflate</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 45층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Trex_Dance · Tiny_Arms · Deflate</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="X15" s="1" t="inlineStr">
         <is>
-          <t>50층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Excavator · Concrete · Joa_Ssu</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 50층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Excavator · Concrete · Joa_Ssu</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="F16" s="1" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="X16" s="1" t="inlineStr">
         <is>
-          <t>55층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Picket · Churu_Raise · Lie_Down</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 55층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Picket · Churu_Raise · Lie_Down</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="F17" s="1" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="X17" s="1" t="inlineStr">
         <is>
-          <t>60층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Gobong · Did_You_Eat · Ladle_Spin</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 60층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Gobong · Did_You_Eat · Ladle_Spin</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="X18" s="1" t="inlineStr">
         <is>
-          <t>65층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Under_The_Sea · Tidal_Wave · Fish_Slap</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 65층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Under_The_Sea · Tidal_Wave · Fish_Slap</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="F19" s="1" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="X19" s="1" t="inlineStr">
         <is>
-          <t>70층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Anchor_Drop · Sonar_Ping · Octo_Ink</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 70층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Anchor_Drop · Sonar_Ping · Octo_Ink</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="X20" s="1" t="inlineStr">
         <is>
-          <t>75층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Baby_Shark · Jaws_Dash · Sharknado</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 75층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Baby_Shark · Jaws_Dash · Sharknado</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="X21" s="1" t="inlineStr">
         <is>
-          <t>80층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Wrong_Way · Barrage · No_Scope</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 80층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Wrong_Way · Barrage · No_Scope</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="F22" s="1" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="X22" s="1" t="inlineStr">
         <is>
-          <t>85층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Lion_Roar · Circle_Of_Life · Supply_Drop</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 85층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Lion_Roar · Circle_Of_Life · Supply_Drop</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="F23" s="1" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="X23" s="1" t="inlineStr">
         <is>
-          <t>90층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Pencil_Throw · Bunker_Rant · Map_Slam</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 90층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Pencil_Throw · Bunker_Rant · Map_Slam</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="F24" s="1" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="X24" s="1" t="inlineStr">
         <is>
-          <t>94층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Vent · Sus · Lights_Out</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 94층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Vent · Sus · Lights_Out</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="F25" s="1" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="X25" s="1" t="inlineStr">
         <is>
-          <t>97층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Laser_Eyes · OIIA · Galaxy_Bang</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 97층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type Laser_Eyes · OIIA · Galaxy_Bang</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="F26" s="1" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -2974,7 +2974,1675 @@
       </c>
       <c r="X26" s="1" t="inlineStr">
         <is>
-          <t>100층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type No_Cat · Had_Fun_Once · Moon_Drop</t>
+          <t>(미사용 2026-10-22: 보스 개편으로 교체, 테스트 패널로만) 100층 보스 (2026-10-19 100층 확장). 기술 = Atk_Type No_Cat · Had_Fun_Once · Moon_Drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>95024</v>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>밈 고양이</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>2995024</v>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>boss_popcat</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>#f3efe6</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R27" s="1" t="inlineStr">
+        <is>
+          <t>R_Maxwell</t>
+        </is>
+      </c>
+      <c r="S27" s="1" t="inlineStr">
+        <is>
+          <t>R_HuhCat</t>
+        </is>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U27" s="1" t="inlineStr">
+        <is>
+          <t>R_HappyDrop</t>
+        </is>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W27" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X27" s="1" t="inlineStr">
+        <is>
+          <t>25층 보스 (보스 개편 2026-10-22). 쿨타임 R_HappyDrop · 발악 R_Maxwell · R_HuhCat</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>95025</v>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>실험체 고양이</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>2995025</v>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>boss_goerem</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>#f0a65a</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q28" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R28" s="1" t="inlineStr">
+        <is>
+          <t>R_SawIt</t>
+        </is>
+      </c>
+      <c r="S28" s="1" t="inlineStr">
+        <is>
+          <t>R_SadBread</t>
+        </is>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U28" s="1" t="inlineStr">
+        <is>
+          <t>R_HairSpit</t>
+        </is>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W28" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X28" s="1" t="inlineStr">
+        <is>
+          <t>30층 보스 (보스 개편 2026-10-22). 쿨타임 R_HairSpit · 발악 R_SawIt · R_SadBread</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>95026</v>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>공룡탈 알바</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>2995011</v>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>boss_dino2</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>#b7804a</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R29" s="1" t="inlineStr">
+        <is>
+          <t>R_TRex</t>
+        </is>
+      </c>
+      <c r="S29" s="1" t="inlineStr">
+        <is>
+          <t>R_Smoke</t>
+        </is>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U29" s="1" t="inlineStr">
+        <is>
+          <t>R_MaskToss</t>
+        </is>
+      </c>
+      <c r="V29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W29" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X29" s="1" t="inlineStr">
+        <is>
+          <t>35층 보스 (보스 개편 2026-10-22). 쿨타임 R_MaskToss · 발악 R_TRex · R_Smoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>95027</v>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>원시인 버티컬 마우스</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>2995027</v>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>boss_vmouse</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>#6f8a5a</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="N30" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O30" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q30" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R30" s="1" t="inlineStr">
+        <is>
+          <t>R_WarCry</t>
+        </is>
+      </c>
+      <c r="S30" s="1" t="inlineStr">
+        <is>
+          <t>R_MouseMeteor</t>
+        </is>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U30" s="1" t="inlineStr">
+        <is>
+          <t>R_ClubSmash</t>
+        </is>
+      </c>
+      <c r="V30" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W30" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X30" s="1" t="inlineStr">
+        <is>
+          <t>40층 보스 (보스 개편 2026-10-22). 쿨타임 R_ClubSmash · 발악 R_WarCry · R_MouseMeteor</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>95028</v>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>랩터 사육사</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>2995010</v>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>boss_trainer</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>#7cb86a</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="N31" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P31" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R31" s="1" t="inlineStr">
+        <is>
+          <t>R_Stampede</t>
+        </is>
+      </c>
+      <c r="S31" s="1" t="inlineStr">
+        <is>
+          <t>R_Whisperer</t>
+        </is>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U31" s="1" t="inlineStr">
+        <is>
+          <t>R_Shotgun</t>
+        </is>
+      </c>
+      <c r="V31" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W31" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X31" s="1" t="inlineStr">
+        <is>
+          <t>45층 보스 (보스 개편 2026-10-22). 쿨타임 R_Shotgun · 발악 R_Stampede · R_Whisperer</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>95029</v>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>노조 고양이</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>2995013</v>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>boss_union2</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>#e0b23a</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="N32" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O32" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R32" s="1" t="inlineStr">
+        <is>
+          <t>R_Solidarity</t>
+        </is>
+      </c>
+      <c r="S32" s="1" t="inlineStr">
+        <is>
+          <t>R_LooksGood</t>
+        </is>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U32" s="1" t="inlineStr">
+        <is>
+          <t>R_PawSlap</t>
+        </is>
+      </c>
+      <c r="V32" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W32" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X32" s="1" t="inlineStr">
+        <is>
+          <t>50층 보스 (보스 개편 2026-10-22). 쿨타임 R_PawSlap · 발악 R_Solidarity · R_LooksGood</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>95030</v>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>거미 고양이</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>2995030</v>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>boss_spider</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J33" s="1" t="inlineStr">
+        <is>
+          <t>#c9564a</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O33" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P33" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R33" s="1" t="inlineStr">
+        <is>
+          <t>R_RebarWeb</t>
+        </is>
+      </c>
+      <c r="S33" s="1" t="inlineStr">
+        <is>
+          <t>R_WebDash</t>
+        </is>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U33" s="1" t="inlineStr">
+        <is>
+          <t>R_RebarSpikes</t>
+        </is>
+      </c>
+      <c r="V33" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W33" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X33" s="1" t="inlineStr">
+        <is>
+          <t>55층 보스 (보스 개편 2026-10-22). 쿨타임 R_RebarSpikes · 발악 R_RebarWeb · R_WebDash</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>95031</v>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>굴착기 기사</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>2995031</v>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>boss_operator</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>#e57b7b</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="N34" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O34" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P34" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R34" s="1" t="inlineStr">
+        <is>
+          <t>R_ExcSpin</t>
+        </is>
+      </c>
+      <c r="S34" s="1" t="inlineStr">
+        <is>
+          <t>R_DiggerDance</t>
+        </is>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U34" s="1" t="inlineStr">
+        <is>
+          <t>R_ConeDrop</t>
+        </is>
+      </c>
+      <c r="V34" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W34" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X34" s="1" t="inlineStr">
+        <is>
+          <t>60층 보스 (보스 개편 2026-10-22). 쿨타임 R_ConeDrop · 발악 R_ExcSpin · R_DiggerDance</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>95032</v>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>상어 고양이</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>2995017</v>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>boss_sharkcat</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>#6cc4c0</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="N35" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O35" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P35" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R35" s="1" t="inlineStr">
+        <is>
+          <t>R_FinRush</t>
+        </is>
+      </c>
+      <c r="S35" s="1" t="inlineStr">
+        <is>
+          <t>R_SneakerTornado</t>
+        </is>
+      </c>
+      <c r="T35" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U35" s="1" t="inlineStr">
+        <is>
+          <t>R_BubbleJail</t>
+        </is>
+      </c>
+      <c r="V35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W35" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X35" s="1" t="inlineStr">
+        <is>
+          <t>65층 보스 (보스 개편 2026-10-22). 쿨타임 R_BubbleJail · 발악 R_FinRush · R_SneakerTornado</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>95033</v>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>머라옹 고양이</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>2995033</v>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>boss_fishcat</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>#c89b4a</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="N36" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O36" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P36" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R36" s="1" t="inlineStr">
+        <is>
+          <t>R_MiniMerlion</t>
+        </is>
+      </c>
+      <c r="S36" s="1" t="inlineStr">
+        <is>
+          <t>R_WaterCannon</t>
+        </is>
+      </c>
+      <c r="T36" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U36" s="1" t="inlineStr">
+        <is>
+          <t>R_BubbleBarrage</t>
+        </is>
+      </c>
+      <c r="V36" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W36" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X36" s="1" t="inlineStr">
+        <is>
+          <t>70층 보스 (보스 개편 2026-10-22). 쿨타임 R_BubbleBarrage · 발악 R_MiniMerlion · R_WaterCannon</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>95034</v>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>심해 잠수부</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>2995034</v>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>boss_deepdiver</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J37" s="1" t="inlineStr">
+        <is>
+          <t>#7f97ad</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L37" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="N37" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O37" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P37" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R37" s="1" t="inlineStr">
+        <is>
+          <t>R_AnchorDrop</t>
+        </is>
+      </c>
+      <c r="S37" s="1" t="inlineStr">
+        <is>
+          <t>R_DepthCharge</t>
+        </is>
+      </c>
+      <c r="T37" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U37" s="1" t="inlineStr">
+        <is>
+          <t>R_Sonar</t>
+        </is>
+      </c>
+      <c r="V37" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W37" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X37" s="1" t="inlineStr">
+        <is>
+          <t>75층 보스 (보스 개편 2026-10-22). 쿨타임 R_Sonar · 발악 R_AnchorDrop · R_DepthCharge</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>95035</v>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>차력거인</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>2995035</v>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>boss_cartgiant</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>#7d8a4e</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M38" s="1" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="N38" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O38" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R38" s="1" t="inlineStr">
+        <is>
+          <t>R_HammerFist</t>
+        </is>
+      </c>
+      <c r="S38" s="1" t="inlineStr">
+        <is>
+          <t>R_StompMarch</t>
+        </is>
+      </c>
+      <c r="T38" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U38" s="1" t="inlineStr">
+        <is>
+          <t>R_MachineGun</t>
+        </is>
+      </c>
+      <c r="V38" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W38" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X38" s="1" t="inlineStr">
+        <is>
+          <t>80층 보스 (보스 개편 2026-10-22). 쿨타임 R_MachineGun · 발악 R_HammerFist · R_StompMarch</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>95036</v>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>항공모함 고양이</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>2995036</v>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>boss_carrier</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J39" s="1" t="inlineStr">
+        <is>
+          <t>#d9a441</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="N39" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O39" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P39" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R39" s="1" t="inlineStr">
+        <is>
+          <t>R_EyeBeam</t>
+        </is>
+      </c>
+      <c r="S39" s="1" t="inlineStr">
+        <is>
+          <t>R_CrocBomber</t>
+        </is>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U39" s="1" t="inlineStr">
+        <is>
+          <t>R_RatSquadron</t>
+        </is>
+      </c>
+      <c r="V39" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W39" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X39" s="1" t="inlineStr">
+        <is>
+          <t>85층 보스 (보스 개편 2026-10-22). 쿨타임 R_RatSquadron · 발악 R_EyeBeam · R_CrocBomber</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>95037</v>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>총통 고양이</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>2995020</v>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>boss_dictator</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>#7a7a7a</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L40" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="N40" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O40" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R40" s="1" t="inlineStr">
+        <is>
+          <t>R_FartGas</t>
+        </is>
+      </c>
+      <c r="S40" s="1" t="inlineStr">
+        <is>
+          <t>R_MustacheToss</t>
+        </is>
+      </c>
+      <c r="T40" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U40" s="1" t="inlineStr">
+        <is>
+          <t>R_ArtToss</t>
+        </is>
+      </c>
+      <c r="V40" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W40" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X40" s="1" t="inlineStr">
+        <is>
+          <t>90층 보스 (보스 개편 2026-10-22). 쿨타임 R_ArtToss · 발악 R_FartGas · R_MustacheToss</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>95038</v>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>그렘린 고양이</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>2995038</v>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>boss_gremlin</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>Hairball</t>
+        </is>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>#d43b3b</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L41" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="N41" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O41" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P41" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R41" s="1" t="inlineStr">
+        <is>
+          <t>R_BabyGremlins</t>
+        </is>
+      </c>
+      <c r="S41" s="1" t="inlineStr">
+        <is>
+          <t>R_Microwave</t>
+        </is>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U41" s="1" t="inlineStr">
+        <is>
+          <t>R_Charge</t>
+        </is>
+      </c>
+      <c r="V41" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W41" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X41" s="1" t="inlineStr">
+        <is>
+          <t>94층 보스 (보스 개편 2026-10-22). 쿨타임 R_Charge · 발악 R_BabyGremlins · R_Microwave</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>95039</v>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>수상한 우주복 쥐</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>2995039</v>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>boss_crewmate</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>#6b4ac8</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M42" s="1" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="N42" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O42" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P42" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R42" s="1" t="inlineStr">
+        <is>
+          <t>R_TentacleGulp</t>
+        </is>
+      </c>
+      <c r="S42" s="1" t="inlineStr">
+        <is>
+          <t>R_Huddle</t>
+        </is>
+      </c>
+      <c r="T42" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U42" s="1" t="inlineStr">
+        <is>
+          <t>R_SirenDrop</t>
+        </is>
+      </c>
+      <c r="V42" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W42" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X42" s="1" t="inlineStr">
+        <is>
+          <t>97층 보스 (보스 개편 2026-10-22). 쿨타임 R_SirenDrop · 발악 R_TentacleGulp · R_Huddle</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>95040</v>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>좋았쓰 고양이 (소환물)</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>2995040</v>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>boss_joassu</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>Swing</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J43" s="1" t="inlineStr">
+        <is>
+          <t>#e39a5a</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L43" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M43" s="1" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="N43" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O43" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P43" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R43" s="1" t="inlineStr"/>
+      <c r="S43" s="1" t="inlineStr"/>
+      <c r="T43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="1" t="inlineStr"/>
+      <c r="V43" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W43" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X43" s="1" t="inlineStr">
+        <is>
+          <t>보스 개편 50층 그림 확인용 (2026-10-22, 행동 미정 → floor 0, 테스트 패널로만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>95041</v>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>굴착기 (탈것)</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>2995041</v>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>boss_excavator</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>Stomp</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
+        <is>
+          <t>Pounce</t>
+        </is>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>#e39a5a</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M44" s="1" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="N44" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="O44" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="P44" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R44" s="1" t="inlineStr"/>
+      <c r="S44" s="1" t="inlineStr"/>
+      <c r="T44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="1" t="inlineStr"/>
+      <c r="V44" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W44" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X44" s="1" t="inlineStr">
+        <is>
+          <t>보스 개편 60층 그림 확인용 (2026-10-22, 행동 미정 → floor 0, 테스트 패널로만)</t>
         </is>
       </c>
     </row>
@@ -8299,7 +9967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S87"/>
+  <dimension ref="A1:U135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8410,6 +10078,16 @@
           <t>패턴 값 2</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>패턴 값 3 (Boss.Rework.cs)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>옵션 키워드 (Boss.Rework.cs)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -8507,6 +10185,16 @@
           <t>p2</t>
         </is>
       </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>opt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -8602,6 +10290,16 @@
       <c r="S3" s="1" t="inlineStr">
         <is>
           <t>float</t>
+        </is>
+      </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -9648,7 +11346,7 @@
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>무한동력 버터 고양이</t>
+          <t>잼 식빵 고양이 회전</t>
         </is>
       </c>
       <c r="I31" s="1" t="n">
@@ -13461,6 +15159,3461 @@
       </c>
       <c r="S87" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>R_HappyDrop</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 해피 고양이 8마리가 떨어져 3초간 폴짝폴짝, 닿으면 1초 기절</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G88" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H88" s="1" t="inlineStr">
+        <is>
+          <t>해피캣 투하</t>
+        </is>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>3100084</v>
+      </c>
+      <c r="J88" s="1" t="n"/>
+      <c r="K88" s="1" t="n"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>bm_happy_mini</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>90</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>#f3efe6</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>해피!</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>4500055</v>
+      </c>
+      <c r="R88" t="n">
+        <v>4</v>
+      </c>
+      <c r="S88" t="n">
+        <v>3</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>R_Maxwell</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 맥스웰 6마리가 바닥 포탈에서 솟아 좌우로 흔들, 닿으면 기절</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G89" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H89" s="1" t="inlineStr">
+        <is>
+          <t>맥스웰 소환</t>
+        </is>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>3100085</v>
+      </c>
+      <c r="J89" s="1" t="n"/>
+      <c r="K89" s="1" t="n"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Rise</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>@maxwell</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>130</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>#c9b49a</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>맥스웰~</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>4500056</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>4</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>R_HuhCat</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 허 고양이 머리 → HUH? 글자가 팝콘처럼 사방 포물선, 착탄 지점 기절</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="1" t="inlineStr">
+        <is>
+          <t>허 고양이</t>
+        </is>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>3100086</v>
+      </c>
+      <c r="J90" s="1" t="n"/>
+      <c r="K90" s="1" t="n"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Throw</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>br_huh_h,br_huh_u,br_huh_h,br_huh_q</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>90</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>#e8c07a</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>HUH?</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>4500057</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>head:br_huh_head,around</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>R_HairSpit</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 몸을 숙이고 입에서 헤어볼이 앞으로 우르르 굴러 나옴</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1" t="inlineStr">
+        <is>
+          <t>헤어볼 뱉기</t>
+        </is>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>3100087</v>
+      </c>
+      <c r="J91" s="1" t="n"/>
+      <c r="K91" s="1" t="n"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>@hairball</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>70</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>#c9a27a</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>켁!</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>4500058</v>
+      </c>
+      <c r="R91" t="n">
+        <v>40</v>
+      </c>
+      <c r="S91" t="n">
+        <v>380</v>
+      </c>
+      <c r="T91" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>R_SawIt</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 목이 길어진 기괴한 얼굴로 바뀌어 그대로 유지 + 빛나며 둘레 기절 (다시 쓰면 빛+기절만)</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>340</v>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H92" s="1" t="inlineStr">
+        <is>
+          <t>너.. 봤구나?</t>
+        </is>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>3100088</v>
+      </c>
+      <c r="J92" s="1" t="inlineStr">
+        <is>
+          <t>너... 봤구나?</t>
+        </is>
+      </c>
+      <c r="K92" s="1" t="n">
+        <v>3200005</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>#f2f0e6</t>
+        </is>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>head_keep:br_goerem_saw</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>R_SadBread</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 식빵으로 변하고 우는 빵 12개 낙하, 맞거나 바닥 반죽에 닿으면 기절</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H93" s="1" t="inlineStr">
+        <is>
+          <t>나 우울해서 빵됐어</t>
+        </is>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>3100089</v>
+      </c>
+      <c r="J93" s="1" t="inlineStr">
+        <is>
+          <t>나 우울해서 빵됐어..</t>
+        </is>
+      </c>
+      <c r="K93" s="1" t="n">
+        <v>3200006</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>br_bread_loaf,br_bread_pizza,br_bread_cake,br_bread_chiffon</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>100</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>#e9c48a</t>
+        </is>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>4</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>body:br_goerem_bread@260,sticky:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>R_MaskToss</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 끙끙 탈을 뽑아 던짐 → 착탄 지점까지 일직선으로 날아가 폭발 (머리엔 탈 그대로)</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="1" t="inlineStr">
+        <is>
+          <t>탈 던지기</t>
+        </is>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>3100090</v>
+      </c>
+      <c r="J94" s="1" t="n"/>
+      <c r="K94" s="1" t="n"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>br_dino_head</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>120</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>#7fb069</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>으랏차!</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>4500059</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>650</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>explode</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>R_TRex</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 공룡처럼 거대화해 걸어다님, 화면 진동 + 둘레 기절</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>티라노 흉내</t>
+        </is>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>3100091</v>
+      </c>
+      <c r="J95" s="1" t="n"/>
+      <c r="K95" s="1" t="n"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Grow</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>#7fb069</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>크아앙!</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>4500060</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>R_Smoke</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 쭈그려 앉아 담배, 퍼지는 연기에 닿으면 기절 (3초 뒤 복귀)</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G96" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H96" s="1" t="inlineStr">
+        <is>
+          <t>현타 담배</t>
+        </is>
+      </c>
+      <c r="I96" s="1" t="n">
+        <v>3100092</v>
+      </c>
+      <c r="J96" s="1" t="n"/>
+      <c r="K96" s="1" t="n"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>br_smoke</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>#b8b8b8</t>
+        </is>
+      </c>
+      <c r="R96" t="n">
+        <v>1</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>body:br_dino_sit@220</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>R_ClubSmash</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 2초간 몽둥이를 마구 휘둘러 범위 쥐를 벽까지 날림</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G97" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t>몽둥이 강타</t>
+        </is>
+      </c>
+      <c r="I97" s="1" t="n">
+        <v>3100093</v>
+      </c>
+      <c r="J97" s="1" t="n"/>
+      <c r="K97" s="1" t="n"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Spin</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>#a07850</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>퍽!</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>4500061</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>R_WarCry</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 몽둥이를 마이크처럼 대고 외침, 음파에 닿으면 기절</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>워크라이</t>
+        </is>
+      </c>
+      <c r="I98" s="1" t="n">
+        <v>3100094</v>
+      </c>
+      <c r="J98" s="1" t="n"/>
+      <c r="K98" s="1" t="n"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Shout</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>br_club</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>120</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>#d9a066</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>우가!!</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>4500062</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>R_MouseMeteor</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 버티컬 마우스 6개 운석 → 크레이터 4초, 닿으면 미니 버티컬 마우스로 3초간 멋대로 (인구 그대로)</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="D99" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H99" s="1" t="inlineStr">
+        <is>
+          <t>버티컬 마우스 투하</t>
+        </is>
+      </c>
+      <c r="I99" s="1" t="n">
+        <v>3100095</v>
+      </c>
+      <c r="J99" s="1" t="n"/>
+      <c r="K99" s="1" t="n"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>br_vmouse_meteor</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>130</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>#8a7a6a</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>쾅!</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>4500038</v>
+      </c>
+      <c r="R99" t="n">
+        <v>5</v>
+      </c>
+      <c r="S99" t="n">
+        <v>4</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>morph:br_vmouse_head@3</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>R_Shotgun</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 장전 1초 → 전방 부채꼴 발사 + 보스 둘레 기절</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="1" t="inlineStr">
+        <is>
+          <t>샷건 발사</t>
+        </is>
+      </c>
+      <c r="I100" s="1" t="n">
+        <v>3100096</v>
+      </c>
+      <c r="J100" s="1" t="n"/>
+      <c r="K100" s="1" t="n"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>br_pellet</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>40</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>#e0c080</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>탕!</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>4500063</v>
+      </c>
+      <c r="R100" t="n">
+        <v>50</v>
+      </c>
+      <c r="S100" t="n">
+        <v>900</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>near</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>R_Stampede</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 랩터 떼가 화면 왼쪽 밖 → 오른쪽 밖, 지나간 뒤 화면 안 쥐 전부 2초 기절</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G101" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H101" s="1" t="inlineStr">
+        <is>
+          <t>랩터 떼</t>
+        </is>
+      </c>
+      <c r="I101" s="1" t="n">
+        <v>3100097</v>
+      </c>
+      <c r="J101" s="1" t="n"/>
+      <c r="K101" s="1" t="n"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Parade</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>bm_raptor</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>150</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>#9ab06a</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>끼아악!</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>4500064</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>R_Whisperer</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 랩터 3마리가 투명→불투명 등장, 5초간 보스 둘레를 돎 (보스는 천천히 걸음)</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H102" s="1" t="inlineStr">
+        <is>
+          <t>랩터 다루기</t>
+        </is>
+      </c>
+      <c r="I102" s="1" t="n">
+        <v>3100098</v>
+      </c>
+      <c r="J102" s="1" t="n"/>
+      <c r="K102" s="1" t="n"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Orbit</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>bm_raptor</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>140</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>#9ab06a</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>진정해!</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>4500065</v>
+      </c>
+      <c r="R102" t="n">
+        <v>240</v>
+      </c>
+      <c r="S102" t="n">
+        <v>70</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>R_PawSlap</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 사냥 자세 1초 → 쥐 무리로 뛰어가 앞발 4연타 (칠 때마다 흔들림 + 기절)</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="1" t="inlineStr">
+        <is>
+          <t>냥냥펀치</t>
+        </is>
+      </c>
+      <c r="I103" s="1" t="n">
+        <v>3100099</v>
+      </c>
+      <c r="J103" s="1" t="n"/>
+      <c r="K103" s="1" t="n"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Slam</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>#e8a0a0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>냥!</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>4500066</v>
+      </c>
+      <c r="R103" t="n">
+        <v>4</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>R_Solidarity</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 두 발로 서서 확성기 → 화면 붉게 깜빡 + 시위대가 화면을 가로지름</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G104" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H104" s="1" t="inlineStr">
+        <is>
+          <t>단결 투쟁</t>
+        </is>
+      </c>
+      <c r="I104" s="1" t="n">
+        <v>3100100</v>
+      </c>
+      <c r="J104" s="1" t="n"/>
+      <c r="K104" s="1" t="n"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Parade</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>bm_picket</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>150</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>#e05050</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>단결 투쟁!</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>4500067</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>red,body:br_union_megaphone@300</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>R_LooksGood</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 안전모 쓰고 전화 → 점점 진동, 먼지 속에서 좋았쓰 고양이들이 사방 포물선</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G105" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>좋았쓰!! 호출</t>
+        </is>
+      </c>
+      <c r="I105" s="1" t="n">
+        <v>3100101</v>
+      </c>
+      <c r="J105" s="1" t="n"/>
+      <c r="K105" s="1" t="n"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Throw</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>bm_joassu</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>110</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>#f0d050</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>좋았쓰!!</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>4500068</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>around,shake,body:br_union_phone@300</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>R_RebarSpikes</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 입을 우물거리다 바라보는 방향 60° 부채꼴로 철근 가시</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="1" t="inlineStr">
+        <is>
+          <t>철근 가시</t>
+        </is>
+      </c>
+      <c r="I106" s="1" t="n">
+        <v>3100102</v>
+      </c>
+      <c r="J106" s="1" t="n"/>
+      <c r="K106" s="1" t="n"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>br_rebar</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>90</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>#8a8f99</t>
+        </is>
+      </c>
+      <c r="R106" t="n">
+        <v>60</v>
+      </c>
+      <c r="S106" t="n">
+        <v>700</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>R_RebarWeb</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 공중에서 큰 철근 거미줄이 낙하 (그림자 예고 1초)</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>360</v>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H107" s="1" t="inlineStr">
+        <is>
+          <t>철근 거미줄</t>
+        </is>
+      </c>
+      <c r="I107" s="1" t="n">
+        <v>3100103</v>
+      </c>
+      <c r="J107" s="1" t="n"/>
+      <c r="K107" s="1" t="n"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>br_rebar_web</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>600</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>#8a8f99</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>철컹!</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>4500069</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>R_WebDash</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 시동 자세 → 3초간 별 + 오각형 모양으로 매우 빠르게 돌진</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G108" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H108" s="1" t="inlineStr">
+        <is>
+          <t>거미줄 돌진</t>
+        </is>
+      </c>
+      <c r="I108" s="1" t="n">
+        <v>3100104</v>
+      </c>
+      <c r="J108" s="1" t="n"/>
+      <c r="K108" s="1" t="n"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>#c0c4cc</t>
+        </is>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>320</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>R_ConeDrop</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 그림자 예고 0.7초 → 라바콘 3개 낙하</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G109" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H109" s="1" t="inlineStr">
+        <is>
+          <t>라바콘 투하</t>
+        </is>
+      </c>
+      <c r="I109" s="1" t="n">
+        <v>3100105</v>
+      </c>
+      <c r="J109" s="1" t="n"/>
+      <c r="K109" s="1" t="n"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>@cone</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>90</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>#f08a30</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>콘!</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>4500070</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>R_ExcSpin</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 굴착기 탑승 → 팔을 펼치고 3초간 빙글빙글</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>330</v>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G110" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H110" s="1" t="inlineStr">
+        <is>
+          <t>굴삭기 회전</t>
+        </is>
+      </c>
+      <c r="I110" s="1" t="n">
+        <v>3100106</v>
+      </c>
+      <c r="J110" s="1" t="n"/>
+      <c r="K110" s="1" t="n"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Spin</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>#f0b030</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>위이잉!</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>4500071</v>
+      </c>
+      <c r="R110" t="n">
+        <v>1</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>ride:boss_excavator</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>R_DiggerDance</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 포크레인 춤추며 사방으로 돌멩이 난사</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G111" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H111" s="1" t="inlineStr">
+        <is>
+          <t>포크레인 댄스</t>
+        </is>
+      </c>
+      <c r="I111" s="1" t="n">
+        <v>3100107</v>
+      </c>
+      <c r="J111" s="1" t="n"/>
+      <c r="K111" s="1" t="n"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>bm_rock</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>60</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>#a08060</t>
+        </is>
+      </c>
+      <c r="R111" t="n">
+        <v>360</v>
+      </c>
+      <c r="S111" t="n">
+        <v>650</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>ride:boss_excavator</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>R_BubbleJail</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 그림자 예고 0.7초 → 3곳에 물방울 감옥 (안의 쥐 1초 갇힘)</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="D112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G112" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H112" s="1" t="inlineStr">
+        <is>
+          <t>물방울 감옥</t>
+        </is>
+      </c>
+      <c r="I112" s="1" t="n">
+        <v>3100108</v>
+      </c>
+      <c r="J112" s="1" t="n"/>
+      <c r="K112" s="1" t="n"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>bm_bubble</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>260</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>#7ec8f0</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>뽀글!</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>4500027</v>
+      </c>
+      <c r="R112" t="n">
+        <v>5</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>R_FinRush</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 몸을 숨기고 붉게 물든 지느러미만 쥐 무리로 돌진</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="D113" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H113" s="1" t="inlineStr">
+        <is>
+          <t>지느러미 돌진</t>
+        </is>
+      </c>
+      <c r="I113" s="1" t="n">
+        <v>3100109</v>
+      </c>
+      <c r="J113" s="1" t="n"/>
+      <c r="K113" s="1" t="n"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>160</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>#e05050</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>빠밤-</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>4500072</v>
+      </c>
+      <c r="R113" t="n">
+        <v>1400</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>hide:bm_fin</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>R_SneakerTornado</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 롤러스케이트 신발로 3초간 바깥 → 안쪽 나선 돌진</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="D114" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G114" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" s="1" t="inlineStr">
+        <is>
+          <t>신발 토네이도</t>
+        </is>
+      </c>
+      <c r="I114" s="1" t="n">
+        <v>3100110</v>
+      </c>
+      <c r="J114" s="1" t="n"/>
+      <c r="K114" s="1" t="n"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>#4a90d9</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>위잉~</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>4500073</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1</v>
+      </c>
+      <c r="S114" t="n">
+        <v>420</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>R_BubbleBarrage</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 바라보는 쪽으로 거품 여러 개</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="D115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F115" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G115" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H115" s="1" t="inlineStr">
+        <is>
+          <t>거품 난사</t>
+        </is>
+      </c>
+      <c r="I115" s="1" t="n">
+        <v>3100111</v>
+      </c>
+      <c r="J115" s="1" t="n"/>
+      <c r="K115" s="1" t="n"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>bm_bubble</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>70</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>#9fd8f5</t>
+        </is>
+      </c>
+      <c r="R115" t="n">
+        <v>30</v>
+      </c>
+      <c r="S115" t="n">
+        <v>450</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>R_MiniMerlion</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 작은 머라옹 3마리가 2초간 돌아다님</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D116" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E116" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F116" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G116" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" s="1" t="inlineStr">
+        <is>
+          <t>꼬마 머라옹 소환</t>
+        </is>
+      </c>
+      <c r="I116" s="1" t="n">
+        <v>3100112</v>
+      </c>
+      <c r="J116" s="1" t="n"/>
+      <c r="K116" s="1" t="n"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>br_mini_merlion</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>110</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>#f0b060</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>머라옹!</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>4500074</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>R_WaterCannon</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 입에서 거대 물줄기, 맞은 쥐 밀려나며 기절</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="D117" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H117" s="1" t="inlineStr">
+        <is>
+          <t>물대포</t>
+        </is>
+      </c>
+      <c r="I117" s="1" t="n">
+        <v>3100113</v>
+      </c>
+      <c r="J117" s="1" t="n"/>
+      <c r="K117" s="1" t="n"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>bm_wave</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>110</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>#5ab0e8</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>촤아아!</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>4500075</v>
+      </c>
+      <c r="R117" t="n">
+        <v>12</v>
+      </c>
+      <c r="S117" t="n">
+        <v>900</v>
+      </c>
+      <c r="T117" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>R_Sonar</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 얼굴에서 음파 파동</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G118" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t>음파 발사</t>
+        </is>
+      </c>
+      <c r="I118" s="1" t="n">
+        <v>3100114</v>
+      </c>
+      <c r="J118" s="1" t="n"/>
+      <c r="K118" s="1" t="n"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>#7fd0e0</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>핑-</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>4500076</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>R_AnchorDrop</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 공중 포탈에서 거대 닻 투하</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H119" s="1" t="inlineStr">
+        <is>
+          <t>닻 투하</t>
+        </is>
+      </c>
+      <c r="I119" s="1" t="n">
+        <v>3100115</v>
+      </c>
+      <c r="J119" s="1" t="n"/>
+      <c r="K119" s="1" t="n"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>bm_anchor</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>240</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>#6a7a8a</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>쿵!</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>4500007</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>R_DepthCharge</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 일직선으로 물기둥 5개가 솟아 쥐를 튕김</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F120" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>폭뢰</t>
+        </is>
+      </c>
+      <c r="I120" s="1" t="n">
+        <v>3100116</v>
+      </c>
+      <c r="J120" s="1" t="n"/>
+      <c r="K120" s="1" t="n"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Sweep</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>bm_wave</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>140</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>#4aa0d0</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>콰앙!</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>4500077</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>R_MachineGun</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 3초간 기관총 사격 (다시 기절 가능)</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="F121" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G121" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H121" s="1" t="inlineStr">
+        <is>
+          <t>기관총 사격</t>
+        </is>
+      </c>
+      <c r="I121" s="1" t="n">
+        <v>3100117</v>
+      </c>
+      <c r="J121" s="1" t="n"/>
+      <c r="K121" s="1" t="n"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>br_bullet</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>30</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>#f0d070</t>
+        </is>
+      </c>
+      <c r="R121" t="n">
+        <v>50</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T121" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>R_HammerFist</t>
+        </is>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 팔을 들었다 바로 앞을 내려침</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G122" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H122" s="1" t="inlineStr">
+        <is>
+          <t>내려찍기</t>
+        </is>
+      </c>
+      <c r="I122" s="1" t="n">
+        <v>3100001</v>
+      </c>
+      <c r="J122" s="1" t="n"/>
+      <c r="K122" s="1" t="n"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Smash</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>#e0b090</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>쾅!!</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>4500078</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>R_StompMarch</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 몸을 일으켜 3초간 크게 쿵쿵 걸으며 둘레 기절</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G123" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H123" s="1" t="inlineStr">
+        <is>
+          <t>쿵쿵 행진</t>
+        </is>
+      </c>
+      <c r="I123" s="1" t="n">
+        <v>3100118</v>
+      </c>
+      <c r="J123" s="1" t="n"/>
+      <c r="K123" s="1" t="n"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Grow</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>#e0b090</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>쿵! 쿵!</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>4500079</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>R_RatSquadron</t>
+        </is>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 활주로에서 쥐 전투기 6대, 5초간 쥐 사이를 날아다님</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F124" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G124" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H124" s="1" t="inlineStr">
+        <is>
+          <t>쥐 전투기 출격</t>
+        </is>
+      </c>
+      <c r="I124" s="1" t="n">
+        <v>3100119</v>
+      </c>
+      <c r="J124" s="1" t="n"/>
+      <c r="K124" s="1" t="n"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>br_rat_jet</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>110</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>#a0b0c0</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>출격!</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>4500080</v>
+      </c>
+      <c r="R124" t="n">
+        <v>420</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>R_EyeBeam</t>
+        </is>
+      </c>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 관제탑 창문 눈에서 빔</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F125" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="1" t="inlineStr">
+        <is>
+          <t>눈깔 빔</t>
+        </is>
+      </c>
+      <c r="I125" s="1" t="n">
+        <v>3100120</v>
+      </c>
+      <c r="J125" s="1" t="n"/>
+      <c r="K125" s="1" t="n"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>#ff5040</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>삐-</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>4500081</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>R_CrocBomber</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 악어 폭격기가 폭탄 6번 투하</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E126" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F126" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G126" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H126" s="1" t="inlineStr">
+        <is>
+          <t>악어 폭격기</t>
+        </is>
+      </c>
+      <c r="I126" s="1" t="n">
+        <v>3100121</v>
+      </c>
+      <c r="J126" s="1" t="n"/>
+      <c r="K126" s="1" t="n"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Sweep</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>bm_shell</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>110</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>#6a9a5a</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>폭격!</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>4500082</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>R_ArtToss</t>
+        </is>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 붓·팔레트·이젤·캔버스를 일직선으로 던짐</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F127" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G127" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>그림 도구 던지기</t>
+        </is>
+      </c>
+      <c r="I127" s="1" t="n">
+        <v>3100122</v>
+      </c>
+      <c r="J127" s="1" t="n"/>
+      <c r="K127" s="1" t="n"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>br_brush,br_palette,br_easel,br_canvas</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>100</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>#c09060</t>
+        </is>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>600</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>R_FartGas</t>
+        </is>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 초록 가스 구름 5초, 기절한 쥐는 5초간 방독면 면역</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G128" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H128" s="1" t="inlineStr">
+        <is>
+          <t>방구가스</t>
+        </is>
+      </c>
+      <c r="I128" s="1" t="n">
+        <v>3100123</v>
+      </c>
+      <c r="J128" s="1" t="n"/>
+      <c r="K128" s="1" t="n"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>@gas</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>#90c050</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>뿌웅~</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>4500083</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T128" t="n">
+        <v>5</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>mask:br_gasmask</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>R_MustacheToss</t>
+        </is>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 수염을 떼어 일직선으로 던짐, 맞은 쥐 밀려남</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="1" t="inlineStr">
+        <is>
+          <t>수염 던지기</t>
+        </is>
+      </c>
+      <c r="I129" s="1" t="n">
+        <v>3100124</v>
+      </c>
+      <c r="J129" s="1" t="n"/>
+      <c r="K129" s="1" t="n"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>br_mustache</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>110</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>#3a3a3a</t>
+        </is>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>750</v>
+      </c>
+      <c r="T129" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>R_Charge</t>
+        </is>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 쥐가 많은 쪽으로 1회 돌진</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G130" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" s="1" t="inlineStr">
+        <is>
+          <t>돌진</t>
+        </is>
+      </c>
+      <c r="I130" s="1" t="n">
+        <v>3100125</v>
+      </c>
+      <c r="J130" s="1" t="n"/>
+      <c r="K130" s="1" t="n"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>#70a050</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>끼햐햐!</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>4500084</v>
+      </c>
+      <c r="R130" t="n">
+        <v>1300</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>R_BabyGremlins</t>
+        </is>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>[발악1] 등에서 새끼 그렘린 6마리, 2초간 돌아다님</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F131" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G131" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t>새끼 그렘린</t>
+        </is>
+      </c>
+      <c r="I131" s="1" t="n">
+        <v>3100126</v>
+      </c>
+      <c r="J131" s="1" t="n"/>
+      <c r="K131" s="1" t="n"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>br_mini_gremlin</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>80</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>#70a050</t>
+        </is>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>R_Microwave</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 하늘에서 거대 전자레인지 → 폭발</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>330</v>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G132" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H132" s="1" t="inlineStr">
+        <is>
+          <t>전자레인지 투하</t>
+        </is>
+      </c>
+      <c r="I132" s="1" t="n">
+        <v>3100127</v>
+      </c>
+      <c r="J132" s="1" t="n"/>
+      <c r="K132" s="1" t="n"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>br_microwave</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>260</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>#c0c0c0</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>띵-! 콰광!</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>4500085</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>R_SirenDrop</t>
+        </is>
+      </c>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>[스킬] 사이렌 4개 낙하, 둘레 1초 기절</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F133" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" s="1" t="inlineStr">
+        <is>
+          <t>사이렌 투하</t>
+        </is>
+      </c>
+      <c r="I133" s="1" t="n">
+        <v>3100128</v>
+      </c>
+      <c r="J133" s="1" t="n"/>
+      <c r="K133" s="1" t="n"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>br_siren</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>90</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>#ff4040</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>삐뽀삐뽀</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>4500086</v>
+      </c>
+      <c r="R133" t="n">
+        <v>5</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>R_TentacleGulp</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>[발악1·등장] 둘레 쥐를 삼켰다 3초 뒤 뱉음 (인구 그대로)</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H134" s="1" t="inlineStr">
+        <is>
+          <t>촉수 삼키기</t>
+        </is>
+      </c>
+      <c r="I134" s="1" t="n">
+        <v>3100129</v>
+      </c>
+      <c r="J134" s="1" t="n"/>
+      <c r="K134" s="1" t="n"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Swallow</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>#c03030</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>꿀꺽!</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>4500087</v>
+      </c>
+      <c r="R134" t="n">
+        <v>3</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>R_Huddle</t>
+        </is>
+      </c>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>[발악2] 빨간 버튼 → 맵의 모든 쥐 2초 멈춤</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" s="1" t="inlineStr">
+        <is>
+          <t>긴급 회의</t>
+        </is>
+      </c>
+      <c r="I135" s="1" t="n">
+        <v>3100130</v>
+      </c>
+      <c r="J135" s="1" t="n"/>
+      <c r="K135" s="1" t="n"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>br_red_button</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>90</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>#ff3030</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>긴급 회의!</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>4500088</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>[발악1] 공중에서 큰 철근 거미줄이 낙하 (그림자 예고 1초)</t>
+          <t>[발악1] 공중에서 큰 철근 거미줄이 낙하 (그림자 예고 1초), 떨어진 자리에 2초 남았다 사라짐</t>
         </is>
       </c>
       <c r="C107" s="1" t="n">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>600</v>
+        <v>720</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -16617,10 +16617,10 @@
         <v>4500069</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T107" t="n">
         <v>0</v>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -4657,7 +4657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9954,6 +9954,258 @@
       </c>
       <c r="E251" s="1" t="n">
         <v>3096353</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>96401</v>
+      </c>
+      <c r="B252" s="1" t="n">
+        <v>95038</v>
+      </c>
+      <c r="C252" s="1" t="inlineStr">
+        <is>
+          <t>Disguise</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t>냐옹~</t>
+        </is>
+      </c>
+      <c r="E252" s="1" t="n">
+        <v>3096401</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>96402</v>
+      </c>
+      <c r="B253" s="1" t="n">
+        <v>95038</v>
+      </c>
+      <c r="C253" s="1" t="inlineStr">
+        <is>
+          <t>Disguise</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="inlineStr">
+        <is>
+          <t>골골골…</t>
+        </is>
+      </c>
+      <c r="E253" s="1" t="n">
+        <v>3096402</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>96403</v>
+      </c>
+      <c r="B254" s="1" t="n">
+        <v>95038</v>
+      </c>
+      <c r="C254" s="1" t="inlineStr">
+        <is>
+          <t>Disguise</t>
+        </is>
+      </c>
+      <c r="D254" s="1" t="inlineStr">
+        <is>
+          <t>부비부비~</t>
+        </is>
+      </c>
+      <c r="E254" s="1" t="n">
+        <v>3096403</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>96404</v>
+      </c>
+      <c r="B255" s="1" t="n">
+        <v>95038</v>
+      </c>
+      <c r="C255" s="1" t="inlineStr">
+        <is>
+          <t>Disguise</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="inlineStr">
+        <is>
+          <t>간식 있어냥?</t>
+        </is>
+      </c>
+      <c r="E255" s="1" t="n">
+        <v>3096404</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>96405</v>
+      </c>
+      <c r="B256" s="1" t="n">
+        <v>95038</v>
+      </c>
+      <c r="C256" s="1" t="inlineStr">
+        <is>
+          <t>Reveal</t>
+        </is>
+      </c>
+      <c r="D256" s="1" t="inlineStr">
+        <is>
+          <t>찌지직…!!</t>
+        </is>
+      </c>
+      <c r="E256" s="1" t="n">
+        <v>3096405</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>96406</v>
+      </c>
+      <c r="B257" s="1" t="n">
+        <v>95038</v>
+      </c>
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>Reveal</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="inlineStr">
+        <is>
+          <t>자정이 지났다냥…</t>
+        </is>
+      </c>
+      <c r="E257" s="1" t="n">
+        <v>3096406</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>96407</v>
+      </c>
+      <c r="B258" s="1" t="n">
+        <v>95039</v>
+      </c>
+      <c r="C258" s="1" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="inlineStr">
+        <is>
+          <t>신화 우주복 쥐 획득!</t>
+        </is>
+      </c>
+      <c r="E258" s="1" t="n">
+        <v>3096407</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>96408</v>
+      </c>
+      <c r="B259" s="1" t="n">
+        <v>95039</v>
+      </c>
+      <c r="C259" s="1" t="inlineStr">
+        <is>
+          <t>Disguise</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t>같이 가자 찍!</t>
+        </is>
+      </c>
+      <c r="E259" s="1" t="n">
+        <v>3096408</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>96409</v>
+      </c>
+      <c r="B260" s="1" t="n">
+        <v>95039</v>
+      </c>
+      <c r="C260" s="1" t="inlineStr">
+        <is>
+          <t>Disguise</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="inlineStr">
+        <is>
+          <t>나 착한 쥐야 찍</t>
+        </is>
+      </c>
+      <c r="E260" s="1" t="n">
+        <v>3096409</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>96410</v>
+      </c>
+      <c r="B261" s="1" t="n">
+        <v>95039</v>
+      </c>
+      <c r="C261" s="1" t="inlineStr">
+        <is>
+          <t>Disguise</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="inlineStr">
+        <is>
+          <t>임무 하는 중~</t>
+        </is>
+      </c>
+      <c r="E261" s="1" t="n">
+        <v>3096410</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>96411</v>
+      </c>
+      <c r="B262" s="1" t="n">
+        <v>95039</v>
+      </c>
+      <c r="C262" s="1" t="inlineStr">
+        <is>
+          <t>Disguise</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="inlineStr">
+        <is>
+          <t>통풍구? 몰라 찍</t>
+        </is>
+      </c>
+      <c r="E262" s="1" t="n">
+        <v>3096411</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>96412</v>
+      </c>
+      <c r="B263" s="1" t="n">
+        <v>95039</v>
+      </c>
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>Reveal</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="inlineStr">
+        <is>
+          <t>사실 나… 임포스터였어!</t>
+        </is>
+      </c>
+      <c r="E263" s="1" t="n">
+        <v>3096412</v>
       </c>
     </row>
   </sheetData>
@@ -18627,7 +18879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18739,6 +18991,42 @@
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>쿨타임 스킬 쓸 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>깜짝 보스 (97층): 동료로 들어올 때 배너</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Disguise</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>깜짝 보스: 변장 중 혼잣말 (94 보통 고양이 · 97 동료 쥐)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Reveal</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>깜짝 보스: 변신할 때 외침 (쥐가 계단에 닿음)</t>
         </is>
       </c>
     </row>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -18650,7 +18650,7 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>[스킬] 사이렌 4개 낙하, 둘레 1초 기절</t>
+          <t>[스킬] 사이렌 4개 낙하, 둘레 1초 기절 · 남아 있는 동안 화면 붉게 깜빡</t>
         </is>
       </c>
       <c r="C133" s="1" t="n">
@@ -18713,6 +18713,11 @@
       <c r="T133" t="n">
         <v>0</v>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>alarm</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -18722,7 +18727,7 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>[발악1·등장] 둘레 쥐를 삼켰다 3초 뒤 뱉음 (인구 그대로)</t>
+          <t>[발악1·등장] 머리가 열리고 혀 촉수 6갈래가 둘레 쥐를 잡아 입으로 → 3초 뒤 한 마리씩 뱉음 (인구 그대로)</t>
         </is>
       </c>
       <c r="C134" s="1" t="n">
@@ -18732,7 +18737,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F134" s="1" t="n">
         <v>1</v>
@@ -18757,7 +18762,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>br_crew_tongue</t>
         </is>
       </c>
       <c r="N134" t="n">
@@ -18799,7 +18804,7 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>[발악2] 빨간 버튼 → 맵의 모든 쥐 2초 멈춤</t>
+          <t>[발악2] 빨간 버튼을 폴짝 눌러 긴급 회의 화면 → 맵의 모든 쥐 2초 멈춤</t>
         </is>
       </c>
       <c r="C135" s="1" t="n">
@@ -18829,7 +18834,7 @@
       <c r="K135" s="1" t="n"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -18838,7 +18843,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -18864,7 +18869,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>all,face:br_crew_face</t>
         </is>
       </c>
     </row>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Boss" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Boss_Line" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Atk_Type" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Situation_Type" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boss_Line" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atk_Type" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Situation_Type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16635,7 +16635,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>red,body:br_union_megaphone@300</t>
+          <t>red,body:br_union_megaphone@300,rig:boss_union2|boss_joassu@1</t>
         </is>
       </c>
     </row>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>[발악2] 안전모 쓰고 전화 → 점점 진동, 먼지 속에서 좋았쓰 고양이들이 사방 포물선</t>
+          <t>[발악2] 안전모 쓰고 전화 → 점점 진동, 먼지 속에서 좋았쓰 고양이들이 사방 포물선 → 착지 후 3초 돌아다니며 닿은 쥐 기절</t>
         </is>
       </c>
       <c r="C105" s="1" t="n">
@@ -16731,14 +16731,14 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T105" t="n">
         <v>0</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>around,shake,body:br_union_phone@300</t>
+          <t>around,shake,dust,body:br_union_phone@300,rig:boss_joassu@0.8</t>
         </is>
       </c>
     </row>

--- a/Data_Table/보스 테이블.xlsx
+++ b/Data_Table/보스 테이블.xlsx
@@ -960,7 +960,7 @@
         <v>2.8</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>28</v>
+        <v>24.3</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>300</v>
@@ -1054,7 +1054,7 @@
         <v>2.8</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>35.3</v>
+        <v>31.9</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>300</v>
@@ -1148,7 +1148,7 @@
         <v>3.4</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>28.1</v>
+        <v>26.4</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>300</v>
@@ -1336,7 +1336,7 @@
         <v>3.8</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>36.1</v>
+        <v>65.7</v>
       </c>
       <c r="N9" s="1" t="n">
         <v>300</v>
@@ -3028,7 +3028,7 @@
         <v>3.4</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>25</v>
+        <v>24.4</v>
       </c>
       <c r="N27" s="1" t="n">
         <v>300</v>
@@ -3122,7 +3122,7 @@
         <v>4</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>25</v>
+        <v>33.1</v>
       </c>
       <c r="N28" s="1" t="n">
         <v>300</v>
@@ -3216,7 +3216,7 @@
         <v>2.9</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="N29" s="1" t="n">
         <v>300</v>
@@ -3310,7 +3310,7 @@
         <v>2.8</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>40.8</v>
+        <v>27.2</v>
       </c>
       <c r="N30" s="1" t="n">
         <v>300</v>
@@ -3404,7 +3404,7 @@
         <v>2.8</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>26.7</v>
+        <v>30.1</v>
       </c>
       <c r="N31" s="1" t="n">
         <v>300</v>
@@ -3498,7 +3498,7 @@
         <v>3.4</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>27.8</v>
+        <v>32.3</v>
       </c>
       <c r="N32" s="1" t="n">
         <v>300</v>
@@ -3592,7 +3592,7 @@
         <v>3.2</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>26.7</v>
+        <v>32</v>
       </c>
       <c r="N33" s="1" t="n">
         <v>300</v>
@@ -3686,7 +3686,7 @@
         <v>2.9</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>28.9</v>
+        <v>35.8</v>
       </c>
       <c r="N34" s="1" t="n">
         <v>300</v>
@@ -3780,7 +3780,7 @@
         <v>3.2</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>26.7</v>
+        <v>34</v>
       </c>
       <c r="N35" s="1" t="n">
         <v>300</v>
@@ -3874,7 +3874,7 @@
         <v>3</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>48.6</v>
+        <v>36.4</v>
       </c>
       <c r="N36" s="1" t="n">
         <v>300</v>
@@ -3968,7 +3968,7 @@
         <v>2.9</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>28.9</v>
+        <v>49.9</v>
       </c>
       <c r="N37" s="1" t="n">
         <v>300</v>
@@ -4062,7 +4062,7 @@
         <v>3.6</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>27.8</v>
+        <v>48.6</v>
       </c>
       <c r="N38" s="1" t="n">
         <v>300</v>
@@ -4156,7 +4156,7 @@
         <v>4.5</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>28.9</v>
+        <v>51.2</v>
       </c>
       <c r="N39" s="1" t="n">
         <v>300</v>
@@ -4250,7 +4250,7 @@
         <v>3.5</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>30.6</v>
+        <v>54.9</v>
       </c>
       <c r="N40" s="1" t="n">
         <v>300</v>
@@ -4344,7 +4344,7 @@
         <v>3.5</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>33.3</v>
+        <v>49.6</v>
       </c>
       <c r="N41" s="1" t="n">
         <v>300</v>
@@ -4438,7 +4438,7 @@
         <v>3.2</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>34.7</v>
+        <v>52.4</v>
       </c>
       <c r="N42" s="1" t="n">
         <v>300</v>
